--- a/research/traditional_assets/database/data/netherlands/netherlands_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_heathcare_information_and_technology.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09663661468084667</v>
+        <v>0.09642068221497009</v>
       </c>
       <c r="C2">
-        <v>11222.36818333625</v>
+        <v>11146.07511803208</v>
       </c>
       <c r="D2">
-        <v>10249.36818333625</v>
+        <v>10293.08887710537</v>
       </c>
       <c r="E2">
-        <v>-2104.275907329155</v>
+        <v>-1984.262148255863</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>120.0137590732916</v>
       </c>
       <c r="G2">
         <v>973</v>
@@ -1451,28 +1451,28 @@
         <v>623.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.036692081386565</v>
       </c>
       <c r="N2">
-        <v>623.1</v>
+        <v>617.0633079186134</v>
       </c>
       <c r="O2">
-        <v>160.7598</v>
+        <v>159.2023334430023</v>
       </c>
       <c r="P2">
-        <v>462.3402</v>
+        <v>457.8609744756112</v>
       </c>
       <c r="Q2">
-        <v>533.9402</v>
+        <v>529.4609744756111</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09663661468084667</v>
+        <v>0.09701763254037382</v>
       </c>
       <c r="T2">
-        <v>1.174055766301309</v>
+        <v>1.182855254973992</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>103.2187813457069</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09642068221497009</v>
+        <v>0.0962047497490935</v>
       </c>
       <c r="C3">
-        <v>11146.07511803208</v>
+        <v>11070.15664906109</v>
       </c>
       <c r="D3">
-        <v>10293.08887710537</v>
+        <v>10337.18416720767</v>
       </c>
       <c r="E3">
-        <v>-1984.262148255863</v>
+        <v>-1864.248389182571</v>
       </c>
       <c r="F3">
-        <v>120.0137590732916</v>
+        <v>240.0275181465831</v>
       </c>
       <c r="G3">
         <v>973</v>
@@ -1533,28 +1533,28 @@
         <v>623.1</v>
       </c>
       <c r="M3">
-        <v>6.036692081386565</v>
+        <v>12.07338416277313</v>
       </c>
       <c r="N3">
-        <v>617.0633079186134</v>
+        <v>611.0266158372269</v>
       </c>
       <c r="O3">
-        <v>159.2023334430023</v>
+        <v>157.6448668860046</v>
       </c>
       <c r="P3">
-        <v>457.8609744756112</v>
+        <v>453.3817489512223</v>
       </c>
       <c r="Q3">
-        <v>529.4609744756111</v>
+        <v>524.9817489512224</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09701763254037382</v>
+        <v>0.09740642627458521</v>
       </c>
       <c r="T3">
-        <v>1.182855254973992</v>
+        <v>1.191834325048158</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>103.2187813457069</v>
+        <v>51.60939067285345</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0962047497490935</v>
+        <v>0.09598881728321691</v>
       </c>
       <c r="C4">
-        <v>11070.15664906109</v>
+        <v>10994.61761141528</v>
       </c>
       <c r="D4">
-        <v>10337.18416720767</v>
+        <v>10381.65888863515</v>
       </c>
       <c r="E4">
-        <v>-1864.248389182571</v>
+        <v>-1744.23463010928</v>
       </c>
       <c r="F4">
-        <v>240.0275181465831</v>
+        <v>360.0412772198746</v>
       </c>
       <c r="G4">
         <v>973</v>
@@ -1615,28 +1615,28 @@
         <v>623.1</v>
       </c>
       <c r="M4">
-        <v>12.07338416277313</v>
+        <v>18.11007624415969</v>
       </c>
       <c r="N4">
-        <v>611.0266158372269</v>
+        <v>604.9899237558403</v>
       </c>
       <c r="O4">
-        <v>157.6448668860046</v>
+        <v>156.0874003290068</v>
       </c>
       <c r="P4">
-        <v>453.3817489512223</v>
+        <v>448.9025234268335</v>
       </c>
       <c r="Q4">
-        <v>524.9817489512224</v>
+        <v>520.5025234268335</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09740642627458521</v>
+        <v>0.09780323637445043</v>
       </c>
       <c r="T4">
-        <v>1.191834325048158</v>
+        <v>1.20099853058777</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>51.60939067285345</v>
+        <v>34.40626044856896</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09598881728321691</v>
+        <v>0.09577288481734034</v>
       </c>
       <c r="C5">
-        <v>10994.61761141528</v>
+        <v>10919.46292365449</v>
       </c>
       <c r="D5">
-        <v>10381.65888863515</v>
+        <v>10426.51795994765</v>
       </c>
       <c r="E5">
-        <v>-1744.23463010928</v>
+        <v>-1624.220871035988</v>
       </c>
       <c r="F5">
-        <v>360.0412772198746</v>
+        <v>480.0550362931662</v>
       </c>
       <c r="G5">
         <v>973</v>
@@ -1697,28 +1697,28 @@
         <v>623.1</v>
       </c>
       <c r="M5">
-        <v>18.11007624415969</v>
+        <v>24.14676832554626</v>
       </c>
       <c r="N5">
-        <v>604.9899237558403</v>
+        <v>598.9532316744537</v>
       </c>
       <c r="O5">
-        <v>156.0874003290068</v>
+        <v>154.5299337720091</v>
       </c>
       <c r="P5">
-        <v>448.9025234268335</v>
+        <v>444.4232979024447</v>
       </c>
       <c r="Q5">
-        <v>520.5025234268335</v>
+        <v>516.0232979024447</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09780323637445043</v>
+        <v>0.09820831335139618</v>
       </c>
       <c r="T5">
-        <v>1.20099853058777</v>
+        <v>1.210353657076125</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.40626044856896</v>
+        <v>25.80469533642672</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09577288481734034</v>
+        <v>0.09555695235146373</v>
       </c>
       <c r="C6">
-        <v>10919.46292365449</v>
+        <v>10844.69758971976</v>
       </c>
       <c r="D6">
-        <v>10426.51795994765</v>
+        <v>10471.76638508621</v>
       </c>
       <c r="E6">
-        <v>-1624.220871035988</v>
+        <v>-1504.207111962697</v>
       </c>
       <c r="F6">
-        <v>480.0550362931662</v>
+        <v>600.0687953664577</v>
       </c>
       <c r="G6">
         <v>973</v>
@@ -1779,28 +1779,28 @@
         <v>623.1</v>
       </c>
       <c r="M6">
-        <v>24.14676832554626</v>
+        <v>30.18346040693282</v>
       </c>
       <c r="N6">
-        <v>598.9532316744537</v>
+        <v>592.9165395930672</v>
       </c>
       <c r="O6">
-        <v>154.5299337720091</v>
+        <v>152.9724672150113</v>
       </c>
       <c r="P6">
-        <v>444.4232979024447</v>
+        <v>439.9440723780559</v>
       </c>
       <c r="Q6">
-        <v>516.0232979024447</v>
+        <v>511.5440723780559</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09820831335139618</v>
+        <v>0.09862191826469868</v>
       </c>
       <c r="T6">
-        <v>1.210353657076125</v>
+        <v>1.219905733595813</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.80469533642672</v>
+        <v>20.64375626914138</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09555695235146373</v>
+        <v>0.09534101988558716</v>
       </c>
       <c r="C7">
-        <v>10844.69758971976</v>
+        <v>10770.32670079402</v>
       </c>
       <c r="D7">
-        <v>10471.76638508621</v>
+        <v>10517.40925523376</v>
       </c>
       <c r="E7">
-        <v>-1504.207111962697</v>
+        <v>-1384.193352889405</v>
       </c>
       <c r="F7">
-        <v>600.0687953664577</v>
+        <v>720.0825544397494</v>
       </c>
       <c r="G7">
         <v>973</v>
@@ -1861,28 +1861,28 @@
         <v>623.1</v>
       </c>
       <c r="M7">
-        <v>30.18346040693282</v>
+        <v>36.22015248831939</v>
       </c>
       <c r="N7">
-        <v>592.9165395930672</v>
+        <v>586.8798475116806</v>
       </c>
       <c r="O7">
-        <v>152.9724672150113</v>
+        <v>151.4150006580136</v>
       </c>
       <c r="P7">
-        <v>439.9440723780559</v>
+        <v>435.464846853667</v>
       </c>
       <c r="Q7">
-        <v>511.5440723780559</v>
+        <v>507.0648468536671</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09862191826469868</v>
+        <v>0.09904432328253954</v>
       </c>
       <c r="T7">
-        <v>1.219905733595813</v>
+        <v>1.229661045786133</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.64375626914138</v>
+        <v>17.20313022428448</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09534101988558716</v>
+        <v>0.0951250874197106</v>
       </c>
       <c r="C8">
-        <v>10770.32670079402</v>
+        <v>10696.35543721173</v>
       </c>
       <c r="D8">
-        <v>10517.40925523376</v>
+        <v>10563.45175072477</v>
       </c>
       <c r="E8">
-        <v>-1384.193352889405</v>
+        <v>-1264.179593816114</v>
       </c>
       <c r="F8">
-        <v>720.0825544397493</v>
+        <v>840.0963135130407</v>
       </c>
       <c r="G8">
         <v>973</v>
@@ -1943,28 +1943,28 @@
         <v>623.1</v>
       </c>
       <c r="M8">
-        <v>36.22015248831939</v>
+        <v>42.25684456970595</v>
       </c>
       <c r="N8">
-        <v>586.8798475116806</v>
+        <v>580.843155430294</v>
       </c>
       <c r="O8">
-        <v>151.4150006580136</v>
+        <v>149.8575341010159</v>
       </c>
       <c r="P8">
-        <v>435.464846853667</v>
+        <v>430.9856213292782</v>
       </c>
       <c r="Q8">
-        <v>507.0648468536671</v>
+        <v>502.5856213292782</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09904432328253954</v>
+        <v>0.0994758122792587</v>
       </c>
       <c r="T8">
-        <v>1.229661045786133</v>
+        <v>1.23962614963646</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.20313022428448</v>
+        <v>14.74554019224384</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09512508741971058</v>
+        <v>0.09490915495383401</v>
       </c>
       <c r="C9">
-        <v>10696.35543721173</v>
+        <v>10622.78907041889</v>
       </c>
       <c r="D9">
-        <v>10563.45175072477</v>
+        <v>10609.89914300523</v>
       </c>
       <c r="E9">
-        <v>-1264.179593816114</v>
+        <v>-1144.165834742822</v>
       </c>
       <c r="F9">
-        <v>840.096313513041</v>
+        <v>960.1100725863324</v>
       </c>
       <c r="G9">
         <v>973</v>
@@ -2025,28 +2025,28 @@
         <v>623.1</v>
       </c>
       <c r="M9">
-        <v>42.25684456970596</v>
+        <v>48.29353665109252</v>
       </c>
       <c r="N9">
-        <v>580.843155430294</v>
+        <v>574.8064633489075</v>
       </c>
       <c r="O9">
-        <v>149.8575341010159</v>
+        <v>148.3000675440181</v>
       </c>
       <c r="P9">
-        <v>430.9856213292782</v>
+        <v>426.5063958048894</v>
       </c>
       <c r="Q9">
-        <v>502.5856213292782</v>
+        <v>498.1063958048894</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0994758122792587</v>
+        <v>0.09991668147155869</v>
       </c>
       <c r="T9">
-        <v>1.23962614963646</v>
+        <v>1.249807886179185</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.74554019224384</v>
+        <v>12.90234766821336</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09490915495383401</v>
+        <v>0.09469322248795743</v>
       </c>
       <c r="C10">
-        <v>10622.78907041889</v>
+        <v>10549.63296498492</v>
       </c>
       <c r="D10">
-        <v>10609.89914300523</v>
+        <v>10656.75679664455</v>
       </c>
       <c r="E10">
-        <v>-1144.165834742822</v>
+        <v>-1024.152075669531</v>
       </c>
       <c r="F10">
-        <v>960.1100725863324</v>
+        <v>1080.123831659624</v>
       </c>
       <c r="G10">
         <v>973</v>
@@ -2107,28 +2107,28 @@
         <v>623.1</v>
       </c>
       <c r="M10">
-        <v>48.29353665109252</v>
+        <v>54.33022873247908</v>
       </c>
       <c r="N10">
-        <v>574.8064633489075</v>
+        <v>568.7697712675209</v>
       </c>
       <c r="O10">
-        <v>148.3000675440181</v>
+        <v>146.7426009870204</v>
       </c>
       <c r="P10">
-        <v>426.5063958048894</v>
+        <v>422.0271702805005</v>
       </c>
       <c r="Q10">
-        <v>498.1063958048894</v>
+        <v>493.6271702805005</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09991668147155869</v>
+        <v>0.1003672400966565</v>
       </c>
       <c r="T10">
-        <v>1.249807886179185</v>
+        <v>1.260213397151421</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.90234766821336</v>
+        <v>11.46875348285632</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09469322248795743</v>
+        <v>0.09447729002208084</v>
       </c>
       <c r="C11">
-        <v>10549.63296498492</v>
+        <v>10476.89258066817</v>
       </c>
       <c r="D11">
-        <v>10656.75679664455</v>
+        <v>10704.03017140108</v>
       </c>
       <c r="E11">
-        <v>-1024.152075669531</v>
+        <v>-904.1383165962391</v>
       </c>
       <c r="F11">
-        <v>1080.123831659624</v>
+        <v>1200.137590732915</v>
       </c>
       <c r="G11">
         <v>973</v>
@@ -2189,28 +2189,28 @@
         <v>623.1</v>
       </c>
       <c r="M11">
-        <v>54.33022873247908</v>
+        <v>60.36692081386565</v>
       </c>
       <c r="N11">
-        <v>568.7697712675209</v>
+        <v>562.7330791861343</v>
       </c>
       <c r="O11">
-        <v>146.7426009870204</v>
+        <v>145.1851344300227</v>
       </c>
       <c r="P11">
-        <v>422.0271702805005</v>
+        <v>417.5479447561116</v>
       </c>
       <c r="Q11">
-        <v>493.6271702805005</v>
+        <v>489.1479447561117</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1003672400966565</v>
+        <v>0.1008278111356454</v>
       </c>
       <c r="T11">
-        <v>1.260213397151421</v>
+        <v>1.270850141700817</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.46875348285632</v>
+        <v>10.32187813457069</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09447729002208084</v>
+        <v>0.09426135755620425</v>
       </c>
       <c r="C12">
-        <v>10476.89258066817</v>
+        <v>10404.5734745366</v>
       </c>
       <c r="D12">
-        <v>10704.03017140108</v>
+        <v>10751.72482434281</v>
       </c>
       <c r="E12">
-        <v>-904.1383165962391</v>
+        <v>-784.1245575229475</v>
       </c>
       <c r="F12">
-        <v>1200.137590732915</v>
+        <v>1320.151349806207</v>
       </c>
       <c r="G12">
         <v>973</v>
@@ -2271,28 +2271,28 @@
         <v>623.1</v>
       </c>
       <c r="M12">
-        <v>60.36692081386565</v>
+        <v>66.40361289525221</v>
       </c>
       <c r="N12">
-        <v>562.7330791861343</v>
+        <v>556.6963871047478</v>
       </c>
       <c r="O12">
-        <v>145.1851344300227</v>
+        <v>143.6276678730249</v>
       </c>
       <c r="P12">
-        <v>417.5479447561116</v>
+        <v>413.0687192317229</v>
       </c>
       <c r="Q12">
-        <v>489.1479447561117</v>
+        <v>484.6687192317229</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1008278111356454</v>
+        <v>0.1012987320856227</v>
       </c>
       <c r="T12">
-        <v>1.270850141700817</v>
+        <v>1.281725914217616</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.32187813457069</v>
+        <v>9.383525576882445</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09426135755620425</v>
+        <v>0.09417898509032767</v>
       </c>
       <c r="C13">
-        <v>10404.5734745366</v>
+        <v>10302.86613682693</v>
       </c>
       <c r="D13">
-        <v>10751.72482434281</v>
+        <v>10770.03124570643</v>
       </c>
       <c r="E13">
-        <v>-784.1245575229475</v>
+        <v>-664.1107984496559</v>
       </c>
       <c r="F13">
-        <v>1320.151349806207</v>
+        <v>1440.165108879499</v>
       </c>
       <c r="G13">
         <v>973</v>
@@ -2353,45 +2353,45 @@
         <v>623.1</v>
       </c>
       <c r="M13">
-        <v>66.40361289525221</v>
+        <v>74.60055263995802</v>
       </c>
       <c r="N13">
-        <v>556.6963871047478</v>
+        <v>548.499447360042</v>
       </c>
       <c r="O13">
-        <v>143.6276678730249</v>
+        <v>141.5128574188909</v>
       </c>
       <c r="P13">
-        <v>413.0687192317229</v>
+        <v>406.9865899411512</v>
       </c>
       <c r="Q13">
-        <v>484.6687192317229</v>
+        <v>478.5865899411511</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1012987320856227</v>
+        <v>0.1017803557844633</v>
       </c>
       <c r="T13">
-        <v>1.281725914217616</v>
+        <v>1.292848863382523</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>9.383525576882445</v>
+        <v>8.352485041327311</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09417898509032767</v>
+        <v>0.09397418262445109</v>
       </c>
       <c r="C14">
-        <v>10302.86613682693</v>
+        <v>10228.63891395464</v>
       </c>
       <c r="D14">
-        <v>10770.03124570643</v>
+        <v>10815.81778190744</v>
       </c>
       <c r="E14">
-        <v>-664.1107984496559</v>
+        <v>-544.0970393763644</v>
       </c>
       <c r="F14">
-        <v>1440.165108879499</v>
+        <v>1560.17886795279</v>
       </c>
       <c r="G14">
         <v>973</v>
@@ -2435,28 +2435,28 @@
         <v>623.1</v>
       </c>
       <c r="M14">
-        <v>74.60055263995802</v>
+        <v>80.81726535995453</v>
       </c>
       <c r="N14">
-        <v>548.499447360042</v>
+        <v>542.2827346400455</v>
       </c>
       <c r="O14">
-        <v>141.5128574188909</v>
+        <v>139.9089455371318</v>
       </c>
       <c r="P14">
-        <v>406.9865899411512</v>
+        <v>402.3737891029137</v>
       </c>
       <c r="Q14">
-        <v>478.5865899411511</v>
+        <v>473.9737891029138</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1017803557844633</v>
+        <v>0.1022730512924725</v>
       </c>
       <c r="T14">
-        <v>1.292848863382523</v>
+        <v>1.304227512528234</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.352485041327311</v>
+        <v>7.709986191994441</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09397418262445109</v>
+        <v>0.0937693801585745</v>
       </c>
       <c r="C15">
-        <v>10228.63891395464</v>
+        <v>10154.80265696464</v>
       </c>
       <c r="D15">
-        <v>10815.81778190744</v>
+        <v>10861.99528399072</v>
       </c>
       <c r="E15">
-        <v>-544.0970393763644</v>
+        <v>-424.0832803030726</v>
       </c>
       <c r="F15">
-        <v>1560.17886795279</v>
+        <v>1680.192627026082</v>
       </c>
       <c r="G15">
         <v>973</v>
@@ -2517,28 +2517,28 @@
         <v>623.1</v>
       </c>
       <c r="M15">
-        <v>80.81726535995453</v>
+        <v>87.03397807995104</v>
       </c>
       <c r="N15">
-        <v>542.2827346400455</v>
+        <v>536.066021920049</v>
       </c>
       <c r="O15">
-        <v>139.9089455371318</v>
+        <v>138.3050336553727</v>
       </c>
       <c r="P15">
-        <v>402.3737891029137</v>
+        <v>397.7609882646764</v>
       </c>
       <c r="Q15">
-        <v>473.9737891029138</v>
+        <v>469.3609882646764</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1022730512924725</v>
+        <v>0.1027772048355517</v>
       </c>
       <c r="T15">
-        <v>1.304227512528234</v>
+        <v>1.315870781421518</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.709986191994441</v>
+        <v>7.159272892566266</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0937693801585745</v>
+        <v>0.09375378769269792</v>
       </c>
       <c r="C16">
-        <v>10154.80265696464</v>
+        <v>10038.32074175533</v>
       </c>
       <c r="D16">
-        <v>10861.99528399072</v>
+        <v>10865.52712785471</v>
       </c>
       <c r="E16">
-        <v>-424.0832803030726</v>
+        <v>-304.069521229781</v>
       </c>
       <c r="F16">
-        <v>1680.192627026082</v>
+        <v>1800.206386099374</v>
       </c>
       <c r="G16">
         <v>973</v>
@@ -2599,45 +2599,45 @@
         <v>623.1</v>
       </c>
       <c r="M16">
-        <v>87.03397807995104</v>
+        <v>96.31104165631648</v>
       </c>
       <c r="N16">
-        <v>536.066021920049</v>
+        <v>526.7889583436836</v>
       </c>
       <c r="O16">
-        <v>138.3050336553727</v>
+        <v>135.9115512526704</v>
       </c>
       <c r="P16">
-        <v>397.7609882646764</v>
+        <v>390.8774070910132</v>
       </c>
       <c r="Q16">
-        <v>469.3609882646764</v>
+        <v>462.4774070910132</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1027772048355517</v>
+        <v>0.1032932208149387</v>
       </c>
       <c r="T16">
-        <v>1.315870781421518</v>
+        <v>1.327788009582881</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.159272892566266</v>
+        <v>6.469663179674837</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09375378769269792</v>
+        <v>0.09356159922682132</v>
       </c>
       <c r="C17">
-        <v>10038.32074175533</v>
+        <v>9962.028906224128</v>
       </c>
       <c r="D17">
-        <v>10865.52712785471</v>
+        <v>10909.24905139679</v>
       </c>
       <c r="E17">
-        <v>-304.0695212297812</v>
+        <v>-184.0557621564897</v>
       </c>
       <c r="F17">
-        <v>1800.206386099373</v>
+        <v>1920.220145172665</v>
       </c>
       <c r="G17">
         <v>973</v>
@@ -2681,28 +2681,28 @@
         <v>623.1</v>
       </c>
       <c r="M17">
-        <v>96.31104165631646</v>
+        <v>102.7317777667376</v>
       </c>
       <c r="N17">
-        <v>526.7889583436836</v>
+        <v>520.3682222332625</v>
       </c>
       <c r="O17">
-        <v>135.9115512526704</v>
+        <v>134.2550013361817</v>
       </c>
       <c r="P17">
-        <v>390.8774070910132</v>
+        <v>386.1132208970807</v>
       </c>
       <c r="Q17">
-        <v>462.4774070910132</v>
+        <v>457.7132208970808</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1032932208149387</v>
+        <v>0.103821522889073</v>
       </c>
       <c r="T17">
-        <v>1.327788009582881</v>
+        <v>1.339988981271894</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.469663179674837</v>
+        <v>6.065309230945159</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09356159922682132</v>
+        <v>0.09336941076094474</v>
       </c>
       <c r="C18">
-        <v>9962.028906224128</v>
+        <v>9886.090358626336</v>
       </c>
       <c r="D18">
-        <v>10909.24905139679</v>
+        <v>10953.32426287229</v>
       </c>
       <c r="E18">
-        <v>-184.0557621564897</v>
+        <v>-64.0420030831981</v>
       </c>
       <c r="F18">
-        <v>1920.220145172665</v>
+        <v>2040.233904245956</v>
       </c>
       <c r="G18">
         <v>973</v>
@@ -2763,28 +2763,28 @@
         <v>623.1</v>
       </c>
       <c r="M18">
-        <v>102.7317777667376</v>
+        <v>109.1525138771587</v>
       </c>
       <c r="N18">
-        <v>520.3682222332625</v>
+        <v>513.9474861228414</v>
       </c>
       <c r="O18">
-        <v>134.2550013361817</v>
+        <v>132.5984514196931</v>
       </c>
       <c r="P18">
-        <v>386.1132208970807</v>
+        <v>381.3490347031483</v>
       </c>
       <c r="Q18">
-        <v>457.7132208970808</v>
+        <v>452.9490347031483</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.103821522889073</v>
+        <v>0.1043625551336684</v>
       </c>
       <c r="T18">
-        <v>1.339988981271894</v>
+        <v>1.352483952278715</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.065309230945159</v>
+        <v>5.708526335007209</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09336941076094474</v>
+        <v>0.09328407029506815</v>
       </c>
       <c r="C19">
-        <v>9886.090358626336</v>
+        <v>9785.76239712015</v>
       </c>
       <c r="D19">
-        <v>10953.32426287229</v>
+        <v>10973.0100604394</v>
       </c>
       <c r="E19">
-        <v>-64.0420030831981</v>
+        <v>55.9717559900937</v>
       </c>
       <c r="F19">
-        <v>2040.233904245956</v>
+        <v>2160.247663319248</v>
       </c>
       <c r="G19">
         <v>973</v>
@@ -2845,45 +2845,45 @@
         <v>623.1</v>
       </c>
       <c r="M19">
-        <v>109.1525138771587</v>
+        <v>117.3014481182352</v>
       </c>
       <c r="N19">
-        <v>513.9474861228414</v>
+        <v>505.7985518817649</v>
       </c>
       <c r="O19">
-        <v>132.5984514196931</v>
+        <v>130.4960263854953</v>
       </c>
       <c r="P19">
-        <v>381.3490347031483</v>
+        <v>375.3025254962695</v>
       </c>
       <c r="Q19">
-        <v>452.9490347031483</v>
+        <v>446.9025254962695</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1043625551336684</v>
+        <v>0.1049167832866685</v>
       </c>
       <c r="T19">
-        <v>1.352483952278715</v>
+        <v>1.365283678675947</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>5.708526335007209</v>
+        <v>5.31195488202277</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09328407029506816</v>
+        <v>0.09309781782919158</v>
       </c>
       <c r="C20">
-        <v>9785.762397120146</v>
+        <v>9708.958880625616</v>
       </c>
       <c r="D20">
-        <v>10973.01006043939</v>
+        <v>11016.22030301816</v>
       </c>
       <c r="E20">
-        <v>55.97175599009324</v>
+        <v>175.9855150633848</v>
       </c>
       <c r="F20">
-        <v>2160.247663319248</v>
+        <v>2280.261422392539</v>
       </c>
       <c r="G20">
         <v>973</v>
@@ -2927,28 +2927,28 @@
         <v>623.1</v>
       </c>
       <c r="M20">
-        <v>117.3014481182352</v>
+        <v>123.8181952359149</v>
       </c>
       <c r="N20">
-        <v>505.7985518817649</v>
+        <v>499.2818047640851</v>
       </c>
       <c r="O20">
-        <v>130.4960263854953</v>
+        <v>128.814705629134</v>
       </c>
       <c r="P20">
-        <v>375.3025254962695</v>
+        <v>370.4670991349511</v>
       </c>
       <c r="Q20">
-        <v>446.9025254962695</v>
+        <v>442.0670991349511</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1049167832866685</v>
+        <v>0.1054846960854217</v>
       </c>
       <c r="T20">
-        <v>1.365283678675947</v>
+        <v>1.37839944770027</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.311954882022771</v>
+        <v>5.03237830928473</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09309781782919158</v>
+        <v>0.09291156536331499</v>
       </c>
       <c r="C21">
-        <v>9708.958880625616</v>
+        <v>9632.497021818295</v>
       </c>
       <c r="D21">
-        <v>11016.22030301816</v>
+        <v>11059.77220328413</v>
       </c>
       <c r="E21">
-        <v>175.9855150633848</v>
+        <v>295.9992741366764</v>
       </c>
       <c r="F21">
-        <v>2280.261422392539</v>
+        <v>2400.275181465831</v>
       </c>
       <c r="G21">
         <v>973</v>
@@ -3009,28 +3009,28 @@
         <v>623.1</v>
       </c>
       <c r="M21">
-        <v>123.8181952359149</v>
+        <v>130.3349423535946</v>
       </c>
       <c r="N21">
-        <v>499.2818047640851</v>
+        <v>492.7650576464054</v>
       </c>
       <c r="O21">
-        <v>128.814705629134</v>
+        <v>127.1333848727726</v>
       </c>
       <c r="P21">
-        <v>370.4670991349511</v>
+        <v>365.6316727736328</v>
       </c>
       <c r="Q21">
-        <v>442.0670991349511</v>
+        <v>437.2316727736328</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1054846960854217</v>
+        <v>0.1060668067041437</v>
       </c>
       <c r="T21">
-        <v>1.37839944770027</v>
+        <v>1.391843110950202</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.03237830928473</v>
+        <v>4.780759393820494</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09291156536331499</v>
+        <v>0.09272531289743841</v>
       </c>
       <c r="C22">
-        <v>9632.497021818295</v>
+        <v>9556.380888945112</v>
       </c>
       <c r="D22">
-        <v>11059.77220328413</v>
+        <v>11103.66982948424</v>
       </c>
       <c r="E22">
-        <v>295.9992741366764</v>
+        <v>416.0130332099684</v>
       </c>
       <c r="F22">
-        <v>2400.275181465831</v>
+        <v>2520.288940539123</v>
       </c>
       <c r="G22">
         <v>973</v>
@@ -3091,28 +3091,28 @@
         <v>623.1</v>
       </c>
       <c r="M22">
-        <v>130.3349423535946</v>
+        <v>136.8516894712744</v>
       </c>
       <c r="N22">
-        <v>492.7650576464054</v>
+        <v>486.2483105287257</v>
       </c>
       <c r="O22">
-        <v>127.1333848727726</v>
+        <v>125.4520641164112</v>
       </c>
       <c r="P22">
-        <v>365.6316727736328</v>
+        <v>360.7962464123144</v>
       </c>
       <c r="Q22">
-        <v>437.2316727736328</v>
+        <v>432.3962464123144</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1060668067041437</v>
+        <v>0.1066636543005549</v>
       </c>
       <c r="T22">
-        <v>1.391843110950202</v>
+        <v>1.405627120105195</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.780759393820494</v>
+        <v>4.553104184590946</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09272531289743841</v>
+        <v>0.09253906043156182</v>
       </c>
       <c r="C23">
-        <v>9556.380888945114</v>
+        <v>9480.614615099923</v>
       </c>
       <c r="D23">
-        <v>11103.66982948424</v>
+        <v>11147.91731471234</v>
       </c>
       <c r="E23">
-        <v>416.0130332099679</v>
+        <v>536.0267922832595</v>
       </c>
       <c r="F23">
-        <v>2520.288940539122</v>
+        <v>2640.302699612414</v>
       </c>
       <c r="G23">
         <v>973</v>
@@ -3173,28 +3173,28 @@
         <v>623.1</v>
       </c>
       <c r="M23">
-        <v>136.8516894712743</v>
+        <v>143.3684365889541</v>
       </c>
       <c r="N23">
-        <v>486.2483105287257</v>
+        <v>479.731563411046</v>
       </c>
       <c r="O23">
-        <v>125.4520641164112</v>
+        <v>123.7707433600499</v>
       </c>
       <c r="P23">
-        <v>360.7962464123145</v>
+        <v>355.9608200509961</v>
       </c>
       <c r="Q23">
-        <v>432.3962464123144</v>
+        <v>427.5608200509961</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1066636543005549</v>
+        <v>0.1072758056814895</v>
       </c>
       <c r="T23">
-        <v>1.405627120105195</v>
+        <v>1.419764565392368</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.553104184590947</v>
+        <v>4.346144903473176</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09253906043156182</v>
+        <v>0.09252346796568524</v>
       </c>
       <c r="C24">
-        <v>9480.614615099923</v>
+        <v>9364.321117554569</v>
       </c>
       <c r="D24">
-        <v>11147.91731471234</v>
+        <v>11151.63757624027</v>
       </c>
       <c r="E24">
-        <v>536.0267922832595</v>
+        <v>656.0405513565511</v>
       </c>
       <c r="F24">
-        <v>2640.302699612414</v>
+        <v>2760.316458685706</v>
       </c>
       <c r="G24">
         <v>973</v>
@@ -3255,45 +3255,45 @@
         <v>623.1</v>
       </c>
       <c r="M24">
-        <v>143.3684365889541</v>
+        <v>152.6455001653195</v>
       </c>
       <c r="N24">
-        <v>479.731563411046</v>
+        <v>470.4544998346805</v>
       </c>
       <c r="O24">
-        <v>123.7707433600499</v>
+        <v>121.3772609573476</v>
       </c>
       <c r="P24">
-        <v>355.9608200509961</v>
+        <v>349.0772388773329</v>
       </c>
       <c r="Q24">
-        <v>427.5608200509961</v>
+        <v>420.6772388773329</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1072758056814895</v>
+        <v>0.1079038570982925</v>
       </c>
       <c r="T24">
-        <v>1.419764565392368</v>
+        <v>1.434269217050636</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.346144903473176</v>
+        <v>4.082006998733435</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09252346796568524</v>
+        <v>0.09234463549980866</v>
       </c>
       <c r="C25">
-        <v>9364.321117554569</v>
+        <v>9287.153861089064</v>
       </c>
       <c r="D25">
-        <v>11151.63757624027</v>
+        <v>11194.48407884806</v>
       </c>
       <c r="E25">
-        <v>656.0405513565511</v>
+        <v>776.0543104298431</v>
       </c>
       <c r="F25">
-        <v>2760.316458685706</v>
+        <v>2880.330217758998</v>
       </c>
       <c r="G25">
         <v>973</v>
@@ -3337,28 +3337,28 @@
         <v>623.1</v>
       </c>
       <c r="M25">
-        <v>152.6455001653195</v>
+        <v>159.2822610420726</v>
       </c>
       <c r="N25">
-        <v>470.4544998346805</v>
+        <v>463.8177389579274</v>
       </c>
       <c r="O25">
-        <v>121.3772609573476</v>
+        <v>119.6649766511453</v>
       </c>
       <c r="P25">
-        <v>349.0772388773329</v>
+        <v>344.1527623067822</v>
       </c>
       <c r="Q25">
-        <v>420.6772388773329</v>
+        <v>415.7527623067822</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1079038570982925</v>
+        <v>0.1085484361839588</v>
       </c>
       <c r="T25">
-        <v>1.434269217050636</v>
+        <v>1.449155570068332</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.082006998733435</v>
+        <v>3.911923373786208</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09234463549980866</v>
+        <v>0.09216580303393207</v>
       </c>
       <c r="C26">
-        <v>9287.153861089064</v>
+        <v>9210.31712173808</v>
       </c>
       <c r="D26">
-        <v>11194.48407884806</v>
+        <v>11237.66109857037</v>
       </c>
       <c r="E26">
-        <v>776.0543104298426</v>
+        <v>896.0680695031342</v>
       </c>
       <c r="F26">
-        <v>2880.330217758997</v>
+        <v>3000.343976832289</v>
       </c>
       <c r="G26">
         <v>973</v>
@@ -3419,28 +3419,28 @@
         <v>623.1</v>
       </c>
       <c r="M26">
-        <v>159.2822610420725</v>
+        <v>165.9190219188256</v>
       </c>
       <c r="N26">
-        <v>463.8177389579275</v>
+        <v>457.1809780811744</v>
       </c>
       <c r="O26">
-        <v>119.6649766511453</v>
+        <v>117.952692344943</v>
       </c>
       <c r="P26">
-        <v>344.1527623067822</v>
+        <v>339.2282857362314</v>
       </c>
       <c r="Q26">
-        <v>415.7527623067822</v>
+        <v>410.8282857362315</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1085484361839588</v>
+        <v>0.1092102040452428</v>
       </c>
       <c r="T26">
-        <v>1.449155570068332</v>
+        <v>1.464438892499833</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.911923373786208</v>
+        <v>3.75544643883476</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09216580303393207</v>
+        <v>0.09198697056805548</v>
       </c>
       <c r="C27">
-        <v>9210.31712173808</v>
+        <v>9133.814738713614</v>
       </c>
       <c r="D27">
-        <v>11237.66109857037</v>
+        <v>11281.17247461919</v>
       </c>
       <c r="E27">
-        <v>896.0680695031342</v>
+        <v>1016.081828576426</v>
       </c>
       <c r="F27">
-        <v>3000.343976832289</v>
+        <v>3120.35773590558</v>
       </c>
       <c r="G27">
         <v>973</v>
@@ -3501,28 +3501,28 @@
         <v>623.1</v>
       </c>
       <c r="M27">
-        <v>165.9190219188256</v>
+        <v>172.5557827955786</v>
       </c>
       <c r="N27">
-        <v>457.1809780811744</v>
+        <v>450.5442172044214</v>
       </c>
       <c r="O27">
-        <v>117.952692344943</v>
+        <v>116.2404080387407</v>
       </c>
       <c r="P27">
-        <v>339.2282857362314</v>
+        <v>334.3038091656807</v>
       </c>
       <c r="Q27">
-        <v>410.8282857362315</v>
+        <v>405.9038091656807</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1092102040452428</v>
+        <v>0.1098898575243993</v>
       </c>
       <c r="T27">
-        <v>1.464438892499833</v>
+        <v>1.480135277699753</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.75544643883476</v>
+        <v>3.611006191187269</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09198697056805548</v>
+        <v>0.0918081381021789</v>
       </c>
       <c r="C28">
-        <v>9133.814738713614</v>
+        <v>9057.650610919351</v>
       </c>
       <c r="D28">
-        <v>11281.17247461919</v>
+        <v>11325.02210589822</v>
       </c>
       <c r="E28">
-        <v>1016.081828576426</v>
+        <v>1136.095587649717</v>
       </c>
       <c r="F28">
-        <v>3120.35773590558</v>
+        <v>3240.371494978872</v>
       </c>
       <c r="G28">
         <v>973</v>
@@ -3583,28 +3583,28 @@
         <v>623.1</v>
       </c>
       <c r="M28">
-        <v>172.5557827955786</v>
+        <v>179.1925436723316</v>
       </c>
       <c r="N28">
-        <v>450.5442172044214</v>
+        <v>443.9074563276684</v>
       </c>
       <c r="O28">
-        <v>116.2404080387407</v>
+        <v>114.5281237325384</v>
       </c>
       <c r="P28">
-        <v>334.3038091656807</v>
+        <v>329.3793325951299</v>
       </c>
       <c r="Q28">
-        <v>405.9038091656807</v>
+        <v>400.9793325951299</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1098898575243993</v>
+        <v>0.1105881316468204</v>
       </c>
       <c r="T28">
-        <v>1.480135277699753</v>
+        <v>1.496261700850356</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.611006191187269</v>
+        <v>3.477265221143297</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0918081381021789</v>
+        <v>0.09162930563630232</v>
       </c>
       <c r="C29">
-        <v>9057.650610919351</v>
+        <v>8981.828698115278</v>
       </c>
       <c r="D29">
-        <v>11325.02210589822</v>
+        <v>11369.21395216744</v>
       </c>
       <c r="E29">
-        <v>1136.095587649717</v>
+        <v>1256.109346723009</v>
       </c>
       <c r="F29">
-        <v>3240.371494978872</v>
+        <v>3360.385254052164</v>
       </c>
       <c r="G29">
         <v>973</v>
@@ -3665,28 +3665,28 @@
         <v>623.1</v>
       </c>
       <c r="M29">
-        <v>179.1925436723316</v>
+        <v>185.8293045490847</v>
       </c>
       <c r="N29">
-        <v>443.9074563276684</v>
+        <v>437.2706954509154</v>
       </c>
       <c r="O29">
-        <v>114.5281237325384</v>
+        <v>112.8158394263362</v>
       </c>
       <c r="P29">
-        <v>329.3793325951299</v>
+        <v>324.4548560245792</v>
       </c>
       <c r="Q29">
-        <v>400.9793325951299</v>
+        <v>396.0548560245792</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1105881316468204</v>
+        <v>0.1113058022726421</v>
       </c>
       <c r="T29">
-        <v>1.496261700850356</v>
+        <v>1.512836080199587</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.477265221143297</v>
+        <v>3.353077177531036</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09162930563630232</v>
+        <v>0.09145047317042573</v>
       </c>
       <c r="C30">
-        <v>8981.828698115278</v>
+        <v>8906.353022109695</v>
       </c>
       <c r="D30">
-        <v>11369.21395216744</v>
+        <v>11413.75203523515</v>
       </c>
       <c r="E30">
-        <v>1256.109346723009</v>
+        <v>1376.123105796301</v>
       </c>
       <c r="F30">
-        <v>3360.385254052164</v>
+        <v>3480.399013125455</v>
       </c>
       <c r="G30">
         <v>973</v>
@@ -3747,28 +3747,28 @@
         <v>623.1</v>
       </c>
       <c r="M30">
-        <v>185.8293045490847</v>
+        <v>192.4660654258377</v>
       </c>
       <c r="N30">
-        <v>437.2706954509154</v>
+        <v>430.6339345741624</v>
       </c>
       <c r="O30">
-        <v>112.8158394263362</v>
+        <v>111.1035551201339</v>
       </c>
       <c r="P30">
-        <v>324.4548560245792</v>
+        <v>319.5303794540285</v>
       </c>
       <c r="Q30">
-        <v>396.0548560245792</v>
+        <v>391.1303794540285</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1113058022726421</v>
+        <v>0.1120436889724306</v>
       </c>
       <c r="T30">
-        <v>1.512836080199587</v>
+        <v>1.529877343474148</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.353077177531036</v>
+        <v>3.23745382658169</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09145047317042573</v>
+        <v>0.09127164070454914</v>
       </c>
       <c r="C31">
-        <v>8906.353022109697</v>
+        <v>8831.22766797933</v>
       </c>
       <c r="D31">
-        <v>11413.75203523515</v>
+        <v>11458.64044017808</v>
       </c>
       <c r="E31">
-        <v>1376.1231057963</v>
+        <v>1496.136864869592</v>
       </c>
       <c r="F31">
-        <v>3480.399013125455</v>
+        <v>3600.412772198747</v>
       </c>
       <c r="G31">
         <v>973</v>
@@ -3829,28 +3829,28 @@
         <v>623.1</v>
       </c>
       <c r="M31">
-        <v>192.4660654258377</v>
+        <v>199.1028263025907</v>
       </c>
       <c r="N31">
-        <v>430.6339345741624</v>
+        <v>423.9971736974093</v>
       </c>
       <c r="O31">
-        <v>111.1035551201339</v>
+        <v>109.3912708139316</v>
       </c>
       <c r="P31">
-        <v>319.5303794540285</v>
+        <v>314.6059028834777</v>
       </c>
       <c r="Q31">
-        <v>391.1303794540285</v>
+        <v>386.2059028834777</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1120436889724306</v>
+        <v>0.1128026581493559</v>
       </c>
       <c r="T31">
-        <v>1.529877343474148</v>
+        <v>1.547405499985125</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.23745382658169</v>
+        <v>3.129538699028967</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09127164070454914</v>
+        <v>0.09109280823867257</v>
       </c>
       <c r="C32">
-        <v>8831.22766797933</v>
+        <v>8756.45678531838</v>
       </c>
       <c r="D32">
-        <v>11458.64044017808</v>
+        <v>11503.88331659042</v>
       </c>
       <c r="E32">
-        <v>1496.136864869592</v>
+        <v>1616.150623942884</v>
       </c>
       <c r="F32">
-        <v>3600.412772198747</v>
+        <v>3720.426531272038</v>
       </c>
       <c r="G32">
         <v>973</v>
@@ -3911,28 +3911,28 @@
         <v>623.1</v>
       </c>
       <c r="M32">
-        <v>199.1028263025907</v>
+        <v>205.7395871793437</v>
       </c>
       <c r="N32">
-        <v>423.9971736974093</v>
+        <v>417.3604128206563</v>
       </c>
       <c r="O32">
-        <v>109.3912708139316</v>
+        <v>107.6789865077293</v>
       </c>
       <c r="P32">
-        <v>314.6059028834777</v>
+        <v>309.681426312927</v>
       </c>
       <c r="Q32">
-        <v>386.2059028834777</v>
+        <v>381.281426312927</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1128026581493559</v>
+        <v>0.1135836264328588</v>
       </c>
       <c r="T32">
-        <v>1.547405499985125</v>
+        <v>1.565441719003668</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.129538699028967</v>
+        <v>3.028585837769968</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09109280823867257</v>
+        <v>0.09150757577279596</v>
       </c>
       <c r="C33">
-        <v>8756.45678531838</v>
+        <v>8532.052512519675</v>
       </c>
       <c r="D33">
-        <v>11503.88331659042</v>
+        <v>11399.492802865</v>
       </c>
       <c r="E33">
-        <v>1616.150623942884</v>
+        <v>1736.164383016175</v>
       </c>
       <c r="F33">
-        <v>3720.426531272038</v>
+        <v>3840.44029034533</v>
       </c>
       <c r="G33">
         <v>973</v>
@@ -3993,45 +3993,45 @@
         <v>623.1</v>
       </c>
       <c r="M33">
-        <v>205.7395871793437</v>
+        <v>221.9774487819601</v>
       </c>
       <c r="N33">
-        <v>417.3604128206563</v>
+        <v>401.1225512180399</v>
       </c>
       <c r="O33">
-        <v>107.6789865077293</v>
+        <v>103.4896182142543</v>
       </c>
       <c r="P33">
-        <v>309.681426312927</v>
+        <v>297.6329330037856</v>
       </c>
       <c r="Q33">
-        <v>381.281426312927</v>
+        <v>369.2329330037857</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1135836264328588</v>
+        <v>0.1143875643717588</v>
       </c>
       <c r="T33">
-        <v>1.565441719003668</v>
+        <v>1.584008415052166</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.028585837769968</v>
+        <v>2.807041901864757</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09150757577279596</v>
+        <v>0.09134729330691939</v>
       </c>
       <c r="C34">
-        <v>8532.052512519675</v>
+        <v>8452.153954230616</v>
       </c>
       <c r="D34">
-        <v>11399.492802865</v>
+        <v>11439.60800364924</v>
       </c>
       <c r="E34">
-        <v>1736.164383016175</v>
+        <v>1856.178142089467</v>
       </c>
       <c r="F34">
-        <v>3840.44029034533</v>
+        <v>3960.454049418621</v>
       </c>
       <c r="G34">
         <v>973</v>
@@ -4075,28 +4075,28 @@
         <v>623.1</v>
       </c>
       <c r="M34">
-        <v>221.9774487819601</v>
+        <v>228.9142440563963</v>
       </c>
       <c r="N34">
-        <v>401.1225512180399</v>
+        <v>394.1857559436037</v>
       </c>
       <c r="O34">
-        <v>103.4896182142543</v>
+        <v>101.6999250334498</v>
       </c>
       <c r="P34">
-        <v>297.6329330037856</v>
+        <v>292.4858309101539</v>
       </c>
       <c r="Q34">
-        <v>369.2329330037857</v>
+        <v>364.085830910154</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1143875643717588</v>
+        <v>0.1152155004580886</v>
       </c>
       <c r="T34">
-        <v>1.584008415052166</v>
+        <v>1.603129340833456</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.807041901864757</v>
+        <v>2.721980026050674</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09134729330691939</v>
+        <v>0.0911870108410428</v>
       </c>
       <c r="C35">
-        <v>8452.153954230616</v>
+        <v>8372.538726488414</v>
       </c>
       <c r="D35">
-        <v>11439.60800364924</v>
+        <v>11480.00653498033</v>
       </c>
       <c r="E35">
-        <v>1856.178142089467</v>
+        <v>1976.191901162758</v>
       </c>
       <c r="F35">
-        <v>3960.454049418621</v>
+        <v>4080.467808491913</v>
       </c>
       <c r="G35">
         <v>973</v>
@@ -4157,28 +4157,28 @@
         <v>623.1</v>
       </c>
       <c r="M35">
-        <v>228.9142440563963</v>
+        <v>235.8510393308326</v>
       </c>
       <c r="N35">
-        <v>394.1857559436037</v>
+        <v>387.2489606691674</v>
       </c>
       <c r="O35">
-        <v>101.6999250334498</v>
+        <v>99.9102318526452</v>
       </c>
       <c r="P35">
-        <v>292.4858309101539</v>
+        <v>287.3387288165222</v>
       </c>
       <c r="Q35">
-        <v>364.085830910154</v>
+        <v>358.9387288165223</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1152155004580886</v>
+        <v>0.1160685255167315</v>
       </c>
       <c r="T35">
-        <v>1.603129340833456</v>
+        <v>1.622829688608119</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.721980026050674</v>
+        <v>2.64192178999036</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0911870108410428</v>
+        <v>0.09102672837516623</v>
       </c>
       <c r="C36">
-        <v>8372.538726488414</v>
+        <v>8293.209841643526</v>
       </c>
       <c r="D36">
-        <v>11480.00653498033</v>
+        <v>11520.69140920873</v>
       </c>
       <c r="E36">
-        <v>1976.191901162758</v>
+        <v>2096.20566023605</v>
       </c>
       <c r="F36">
-        <v>4080.467808491913</v>
+        <v>4200.481567565204</v>
       </c>
       <c r="G36">
         <v>973</v>
@@ -4239,28 +4239,28 @@
         <v>623.1</v>
       </c>
       <c r="M36">
-        <v>235.8510393308326</v>
+        <v>242.7878346052688</v>
       </c>
       <c r="N36">
-        <v>387.2489606691674</v>
+        <v>380.3121653947312</v>
       </c>
       <c r="O36">
-        <v>99.9102318526452</v>
+        <v>98.12053867184065</v>
       </c>
       <c r="P36">
-        <v>287.3387288165222</v>
+        <v>282.1916267228905</v>
       </c>
       <c r="Q36">
-        <v>358.9387288165223</v>
+        <v>353.7916267228906</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1160685255167315</v>
+        <v>0.1169477975002557</v>
       </c>
       <c r="T36">
-        <v>1.622829688608119</v>
+        <v>1.643136200929694</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.64192178999036</v>
+        <v>2.56643831027635</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09102672837516623</v>
+        <v>0.09180136590928964</v>
       </c>
       <c r="C37">
-        <v>8293.209841643526</v>
+        <v>7979.194017452774</v>
       </c>
       <c r="D37">
-        <v>11520.69140920873</v>
+        <v>11326.68934409127</v>
       </c>
       <c r="E37">
-        <v>2096.20566023605</v>
+        <v>2216.219419309342</v>
       </c>
       <c r="F37">
-        <v>4200.481567565204</v>
+        <v>4320.495326638496</v>
       </c>
       <c r="G37">
         <v>973</v>
@@ -4321,45 +4321,45 @@
         <v>623.1</v>
       </c>
       <c r="M37">
-        <v>242.7878346052688</v>
+        <v>264.8463635229398</v>
       </c>
       <c r="N37">
-        <v>380.3121653947312</v>
+        <v>358.2536364770602</v>
       </c>
       <c r="O37">
-        <v>98.12053867184065</v>
+        <v>92.42943821108153</v>
       </c>
       <c r="P37">
-        <v>282.1916267228905</v>
+        <v>265.8241982659787</v>
       </c>
       <c r="Q37">
-        <v>353.7916267228906</v>
+        <v>337.4241982659787</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1169477975002557</v>
+        <v>0.1178545467332651</v>
       </c>
       <c r="T37">
-        <v>1.643136200929694</v>
+        <v>1.664077291761318</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.258</v>
       </c>
       <c r="W37">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.56643831027635</v>
+        <v>2.352684747910574</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09180136590928964</v>
+        <v>0.09166705344341305</v>
       </c>
       <c r="C38">
-        <v>7979.194017452774</v>
+        <v>7892.34819618695</v>
       </c>
       <c r="D38">
-        <v>11326.68934409127</v>
+        <v>11359.85728189874</v>
       </c>
       <c r="E38">
-        <v>2216.219419309341</v>
+        <v>2336.233178382633</v>
       </c>
       <c r="F38">
-        <v>4320.495326638495</v>
+        <v>4440.509085711788</v>
       </c>
       <c r="G38">
         <v>973</v>
@@ -4403,28 +4403,28 @@
         <v>623.1</v>
       </c>
       <c r="M38">
-        <v>264.8463635229398</v>
+        <v>272.2032069541326</v>
       </c>
       <c r="N38">
-        <v>358.2536364770602</v>
+        <v>350.8967930458675</v>
       </c>
       <c r="O38">
-        <v>92.42943821108155</v>
+        <v>90.53137260583381</v>
       </c>
       <c r="P38">
-        <v>265.8241982659787</v>
+        <v>260.3654204400336</v>
       </c>
       <c r="Q38">
-        <v>337.4241982659787</v>
+        <v>331.9654204400337</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1178545467332651</v>
+        <v>0.1187900816562112</v>
       </c>
       <c r="T38">
-        <v>1.664077291761318</v>
+        <v>1.68568317912728</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.352684747910575</v>
+        <v>2.289098673642721</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09166705344341305</v>
+        <v>0.09232222897753647</v>
       </c>
       <c r="C39">
-        <v>7892.34819618695</v>
+        <v>7612.352838514254</v>
       </c>
       <c r="D39">
-        <v>11359.85728189874</v>
+        <v>11199.87568329933</v>
       </c>
       <c r="E39">
-        <v>2336.233178382633</v>
+        <v>2456.246937455924</v>
       </c>
       <c r="F39">
-        <v>4440.509085711788</v>
+        <v>4560.522844785079</v>
       </c>
       <c r="G39">
         <v>973</v>
@@ -4485,45 +4485,45 @@
         <v>623.1</v>
       </c>
       <c r="M39">
-        <v>272.2032069541326</v>
+        <v>292.3295143507236</v>
       </c>
       <c r="N39">
-        <v>350.8967930458675</v>
+        <v>330.7704856492765</v>
       </c>
       <c r="O39">
-        <v>90.53137260583381</v>
+        <v>85.33878529751333</v>
       </c>
       <c r="P39">
-        <v>260.3654204400336</v>
+        <v>245.4317003517631</v>
       </c>
       <c r="Q39">
-        <v>331.9654204400337</v>
+        <v>317.0317003517631</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1187900816562112</v>
+        <v>0.1197557951250588</v>
       </c>
       <c r="T39">
-        <v>1.68568317912728</v>
+        <v>1.707986030601821</v>
       </c>
       <c r="U39">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.258</v>
       </c>
       <c r="W39">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.289098673642721</v>
+        <v>2.131498769065217</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09232222897753647</v>
+        <v>0.09220869251165988</v>
       </c>
       <c r="C40">
-        <v>7612.352838514254</v>
+        <v>7519.738996019511</v>
       </c>
       <c r="D40">
-        <v>11199.87568329933</v>
+        <v>11227.27559987788</v>
       </c>
       <c r="E40">
-        <v>2456.246937455924</v>
+        <v>2576.260696529216</v>
       </c>
       <c r="F40">
-        <v>4560.522844785079</v>
+        <v>4680.536603858371</v>
       </c>
       <c r="G40">
         <v>973</v>
@@ -4567,28 +4567,28 @@
         <v>623.1</v>
       </c>
       <c r="M40">
-        <v>292.3295143507236</v>
+        <v>300.0223963073216</v>
       </c>
       <c r="N40">
-        <v>330.7704856492765</v>
+        <v>323.0776036926785</v>
       </c>
       <c r="O40">
-        <v>85.33878529751333</v>
+        <v>83.35402175271105</v>
       </c>
       <c r="P40">
-        <v>245.4317003517631</v>
+        <v>239.7235819399674</v>
       </c>
       <c r="Q40">
-        <v>317.0317003517631</v>
+        <v>311.3235819399674</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1197557951250588</v>
+        <v>0.12075317133059</v>
       </c>
       <c r="T40">
-        <v>1.707986030601821</v>
+        <v>1.731020123108314</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.131498769065217</v>
+        <v>2.076844954473801</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09220869251165988</v>
+        <v>0.09209515604578332</v>
       </c>
       <c r="C41">
-        <v>7519.738996019511</v>
+        <v>7427.259547269564</v>
       </c>
       <c r="D41">
-        <v>11227.27559987788</v>
+        <v>11254.80991020123</v>
       </c>
       <c r="E41">
-        <v>2576.260696529216</v>
+        <v>2696.274455602507</v>
       </c>
       <c r="F41">
-        <v>4680.536603858371</v>
+        <v>4800.550362931662</v>
       </c>
       <c r="G41">
         <v>973</v>
@@ -4649,28 +4649,28 @@
         <v>623.1</v>
       </c>
       <c r="M41">
-        <v>300.0223963073216</v>
+        <v>307.7152782639195</v>
       </c>
       <c r="N41">
-        <v>323.0776036926785</v>
+        <v>315.3847217360805</v>
       </c>
       <c r="O41">
-        <v>83.35402175271105</v>
+        <v>81.36925820790877</v>
       </c>
       <c r="P41">
-        <v>239.7235819399674</v>
+        <v>234.0154635281717</v>
       </c>
       <c r="Q41">
-        <v>311.3235819399674</v>
+        <v>305.6154635281717</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.12075317133059</v>
+        <v>0.1217837934096389</v>
       </c>
       <c r="T41">
-        <v>1.731020123108314</v>
+        <v>1.754822018698357</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.076844954473801</v>
+        <v>2.024923830611956</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09209515604578332</v>
+        <v>0.09435453557990672</v>
       </c>
       <c r="C42">
-        <v>7427.259547269564</v>
+        <v>6783.527728331211</v>
       </c>
       <c r="D42">
-        <v>11254.80991020123</v>
+        <v>10731.09185033616</v>
       </c>
       <c r="E42">
-        <v>2696.274455602507</v>
+        <v>2816.288214675799</v>
       </c>
       <c r="F42">
-        <v>4800.550362931662</v>
+        <v>4920.564122004954</v>
       </c>
       <c r="G42">
         <v>973</v>
@@ -4731,45 +4731,45 @@
         <v>623.1</v>
       </c>
       <c r="M42">
-        <v>307.7152782639195</v>
+        <v>353.7885603721562</v>
       </c>
       <c r="N42">
-        <v>315.3847217360805</v>
+        <v>269.3114396278438</v>
       </c>
       <c r="O42">
-        <v>81.36925820790877</v>
+        <v>69.4823514239837</v>
       </c>
       <c r="P42">
-        <v>234.0154635281717</v>
+        <v>199.8290882038601</v>
       </c>
       <c r="Q42">
-        <v>305.6154635281717</v>
+        <v>271.4290882038601</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1217837934096389</v>
+        <v>0.1228493518303504</v>
       </c>
       <c r="T42">
-        <v>1.754822018698357</v>
+        <v>1.779430758206706</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.258</v>
       </c>
       <c r="W42">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.024923830611956</v>
+        <v>1.761221446347927</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09435453557990672</v>
+        <v>0.09551427111403013</v>
       </c>
       <c r="C43">
-        <v>6783.527728331211</v>
+        <v>6413.178838924191</v>
       </c>
       <c r="D43">
-        <v>10731.09185033616</v>
+        <v>10480.75672000244</v>
       </c>
       <c r="E43">
-        <v>2816.288214675799</v>
+        <v>2936.301973749091</v>
       </c>
       <c r="F43">
-        <v>4920.564122004954</v>
+        <v>5040.577881078246</v>
       </c>
       <c r="G43">
         <v>973</v>
@@ -4813,45 +4813,45 @@
         <v>623.1</v>
       </c>
       <c r="M43">
-        <v>353.7885603721562</v>
+        <v>382.0758033857311</v>
       </c>
       <c r="N43">
-        <v>269.3114396278438</v>
+        <v>241.0241966142689</v>
       </c>
       <c r="O43">
-        <v>69.4823514239837</v>
+        <v>62.18424272648139</v>
       </c>
       <c r="P43">
-        <v>199.8290882038601</v>
+        <v>178.8399538877875</v>
       </c>
       <c r="Q43">
-        <v>271.4290882038601</v>
+        <v>250.4399538877875</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1228493518303504</v>
+        <v>0.1239516536448795</v>
       </c>
       <c r="T43">
-        <v>1.779430758206706</v>
+        <v>1.804888074939482</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.258</v>
       </c>
       <c r="W43">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.761221446347927</v>
+        <v>1.630828213873933</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09551427111403013</v>
+        <v>0.09548754864815356</v>
       </c>
       <c r="C44">
-        <v>6413.178838924192</v>
+        <v>6298.801736748468</v>
       </c>
       <c r="D44">
-        <v>10480.75672000244</v>
+        <v>10486.39337690001</v>
       </c>
       <c r="E44">
-        <v>2936.30197374909</v>
+        <v>3056.315732822382</v>
       </c>
       <c r="F44">
-        <v>5040.577881078245</v>
+        <v>5160.591640151537</v>
       </c>
       <c r="G44">
         <v>973</v>
@@ -4895,28 +4895,28 @@
         <v>623.1</v>
       </c>
       <c r="M44">
-        <v>382.075803385731</v>
+        <v>391.1728463234865</v>
       </c>
       <c r="N44">
-        <v>241.024196614269</v>
+        <v>231.9271536765135</v>
       </c>
       <c r="O44">
-        <v>62.18424272648141</v>
+        <v>59.83720564854049</v>
       </c>
       <c r="P44">
-        <v>178.8399538877876</v>
+        <v>172.089948027973</v>
       </c>
       <c r="Q44">
-        <v>250.4399538877876</v>
+        <v>243.689948027973</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1239516536448795</v>
+        <v>0.1250926327160589</v>
       </c>
       <c r="T44">
-        <v>1.804888074939482</v>
+        <v>1.831238630855863</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.630828213873934</v>
+        <v>1.592901976341982</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09548754864815356</v>
+        <v>0.09546082618227697</v>
       </c>
       <c r="C45">
-        <v>6298.801736748468</v>
+        <v>6184.4307007373</v>
       </c>
       <c r="D45">
-        <v>10486.39337690001</v>
+        <v>10492.03609996213</v>
       </c>
       <c r="E45">
-        <v>3056.315732822382</v>
+        <v>3176.329491895674</v>
       </c>
       <c r="F45">
-        <v>5160.591640151537</v>
+        <v>5280.605399224828</v>
       </c>
       <c r="G45">
         <v>973</v>
@@ -4977,28 +4977,28 @@
         <v>623.1</v>
       </c>
       <c r="M45">
-        <v>391.1728463234865</v>
+        <v>400.269889261242</v>
       </c>
       <c r="N45">
-        <v>231.9271536765135</v>
+        <v>222.830110738758</v>
       </c>
       <c r="O45">
-        <v>59.83720564854049</v>
+        <v>57.49016857059957</v>
       </c>
       <c r="P45">
-        <v>172.089948027973</v>
+        <v>165.3399421681585</v>
       </c>
       <c r="Q45">
-        <v>243.689948027973</v>
+        <v>236.9399421681585</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1250926327160589</v>
+        <v>0.1262743610397803</v>
       </c>
       <c r="T45">
-        <v>1.831238630855863</v>
+        <v>1.858530278054972</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.592901976341982</v>
+        <v>1.556699658697846</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09546082618227697</v>
+        <v>0.09543410371640039</v>
       </c>
       <c r="C46">
-        <v>6184.4307007373</v>
+        <v>6070.065740688547</v>
       </c>
       <c r="D46">
-        <v>10492.03609996213</v>
+        <v>10497.68489898667</v>
       </c>
       <c r="E46">
-        <v>3176.329491895674</v>
+        <v>3296.343250968966</v>
       </c>
       <c r="F46">
-        <v>5280.605399224828</v>
+        <v>5400.61915829812</v>
       </c>
       <c r="G46">
         <v>973</v>
@@ -5059,28 +5059,28 @@
         <v>623.1</v>
       </c>
       <c r="M46">
-        <v>400.269889261242</v>
+        <v>409.3669321989975</v>
       </c>
       <c r="N46">
-        <v>222.830110738758</v>
+        <v>213.7330678010025</v>
       </c>
       <c r="O46">
-        <v>57.49016857059957</v>
+        <v>55.14313149265865</v>
       </c>
       <c r="P46">
-        <v>165.3399421681585</v>
+        <v>158.5899363083439</v>
       </c>
       <c r="Q46">
-        <v>236.9399421681585</v>
+        <v>230.1899363083438</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1262743610397803</v>
+        <v>0.1274990613025462</v>
       </c>
       <c r="T46">
-        <v>1.858530278054972</v>
+        <v>1.886814348788595</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.556699658697846</v>
+        <v>1.522106332949005</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09543410371640039</v>
+        <v>0.1002541252505238</v>
       </c>
       <c r="C47">
-        <v>6070.065740688547</v>
+        <v>5020.846580945063</v>
       </c>
       <c r="D47">
-        <v>10497.68489898667</v>
+        <v>9568.479498316474</v>
       </c>
       <c r="E47">
-        <v>3296.343250968966</v>
+        <v>3416.357010042257</v>
       </c>
       <c r="F47">
-        <v>5400.61915829812</v>
+        <v>5520.632917371411</v>
       </c>
       <c r="G47">
         <v>973</v>
@@ -5141,45 +5141,45 @@
         <v>623.1</v>
       </c>
       <c r="M47">
-        <v>409.3669321989975</v>
+        <v>496.856962563427</v>
       </c>
       <c r="N47">
-        <v>213.7330678010025</v>
+        <v>126.243037436573</v>
       </c>
       <c r="O47">
-        <v>55.14313149265865</v>
+        <v>32.57070365863585</v>
       </c>
       <c r="P47">
-        <v>158.5899363083439</v>
+        <v>93.6723337779372</v>
       </c>
       <c r="Q47">
-        <v>230.1899363083438</v>
+        <v>165.2723337779372</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1274990613025462</v>
+        <v>0.1287691208343033</v>
       </c>
       <c r="T47">
-        <v>1.886814348788595</v>
+        <v>1.916145977697537</v>
       </c>
       <c r="U47">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V47">
         <v>0.258</v>
       </c>
       <c r="W47">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.522106332949005</v>
+        <v>1.25408326127755</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1002541252505238</v>
+        <v>0.1117158289176815</v>
       </c>
       <c r="C48">
-        <v>5020.846580945063</v>
+        <v>3237.027961100935</v>
       </c>
       <c r="D48">
-        <v>9568.479498316474</v>
+        <v>7904.67463754564</v>
       </c>
       <c r="E48">
-        <v>3416.357010042257</v>
+        <v>3536.370769115549</v>
       </c>
       <c r="F48">
-        <v>5520.632917371411</v>
+        <v>5640.646676444703</v>
       </c>
       <c r="G48">
         <v>973</v>
@@ -5223,45 +5223,45 @@
         <v>623.1</v>
       </c>
       <c r="M48">
-        <v>496.856962563427</v>
+        <v>668.9806958263418</v>
       </c>
       <c r="N48">
-        <v>126.243037436573</v>
+        <v>-45.88069582634182</v>
       </c>
       <c r="O48">
-        <v>32.57070365863585</v>
+        <v>-11.83721952319619</v>
       </c>
       <c r="P48">
-        <v>93.6723337779372</v>
+        <v>-34.04347630314563</v>
       </c>
       <c r="Q48">
-        <v>165.2723337779372</v>
+        <v>37.55652369685436</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1287691208343033</v>
+        <v>0.1308847982038476</v>
       </c>
       <c r="T48">
-        <v>1.916145977697537</v>
+        <v>1.965006886924888</v>
       </c>
       <c r="U48">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V48">
-        <v>0.258</v>
+        <v>0.240305588790459</v>
       </c>
       <c r="W48">
-        <v>0.06677999999999999</v>
+        <v>0.09009975716945158</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.25408326127755</v>
+        <v>0.9314170108157324</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1117158289176815</v>
+        <v>0.1124438289176815</v>
       </c>
       <c r="C49">
-        <v>3237.027961100935</v>
+        <v>3030.665574861558</v>
       </c>
       <c r="D49">
-        <v>7904.67463754564</v>
+        <v>7818.326010379553</v>
       </c>
       <c r="E49">
-        <v>3536.370769115549</v>
+        <v>3656.384528188841</v>
       </c>
       <c r="F49">
-        <v>5640.646676444703</v>
+        <v>5760.660435517995</v>
       </c>
       <c r="G49">
         <v>973</v>
@@ -5305,37 +5305,37 @@
         <v>623.1</v>
       </c>
       <c r="M49">
-        <v>668.9806958263418</v>
+        <v>683.2143276524343</v>
       </c>
       <c r="N49">
-        <v>-45.88069582634182</v>
+        <v>-60.11432765243433</v>
       </c>
       <c r="O49">
-        <v>-11.83721952319619</v>
+        <v>-15.50949653432806</v>
       </c>
       <c r="P49">
-        <v>-34.04347630314563</v>
+        <v>-44.60483111810627</v>
       </c>
       <c r="Q49">
-        <v>37.55652369685436</v>
+        <v>26.99516888189373</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1308847982038476</v>
+        <v>0.1325210443231524</v>
       </c>
       <c r="T49">
-        <v>1.965006886924888</v>
+        <v>2.002795480904213</v>
       </c>
       <c r="U49">
         <v>0.1186</v>
       </c>
       <c r="V49">
-        <v>0.240305588790459</v>
+        <v>0.2352992223573244</v>
       </c>
       <c r="W49">
-        <v>0.09009975716945158</v>
+        <v>0.09069351222842134</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.9314170108157324</v>
+        <v>0.9120124897570712</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1124438289176815</v>
+        <v>0.1131718289176815</v>
       </c>
       <c r="C50">
-        <v>3030.665574861562</v>
+        <v>2826.169303928442</v>
       </c>
       <c r="D50">
-        <v>7818.326010379556</v>
+        <v>7733.843498519726</v>
       </c>
       <c r="E50">
-        <v>3656.38452818884</v>
+        <v>3776.398287262131</v>
       </c>
       <c r="F50">
-        <v>5760.660435517994</v>
+        <v>5880.674194591285</v>
       </c>
       <c r="G50">
         <v>973</v>
@@ -5387,37 +5387,37 @@
         <v>623.1</v>
       </c>
       <c r="M50">
-        <v>683.2143276524342</v>
+        <v>697.4479594785265</v>
       </c>
       <c r="N50">
-        <v>-60.11432765243421</v>
+        <v>-74.34795947852649</v>
       </c>
       <c r="O50">
-        <v>-15.50949653432803</v>
+        <v>-19.18177354545983</v>
       </c>
       <c r="P50">
-        <v>-44.60483111810618</v>
+        <v>-55.16618593306666</v>
       </c>
       <c r="Q50">
-        <v>26.99516888189381</v>
+        <v>16.43381406693334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1325210443231524</v>
+        <v>0.1342214569569397</v>
       </c>
       <c r="T50">
-        <v>2.002795480904212</v>
+        <v>2.042065980529785</v>
       </c>
       <c r="U50">
         <v>0.1186</v>
       </c>
       <c r="V50">
-        <v>0.2352992223573244</v>
+        <v>0.2304971974112566</v>
       </c>
       <c r="W50">
-        <v>0.09069351222842134</v>
+        <v>0.09126303238702498</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.9120124897570713</v>
+        <v>0.8933999899661108</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1131718289176815</v>
+        <v>0.1138998289176815</v>
       </c>
       <c r="C51">
-        <v>2826.169303928442</v>
+        <v>2623.479300929075</v>
       </c>
       <c r="D51">
-        <v>7733.843498519726</v>
+        <v>7651.167254593652</v>
       </c>
       <c r="E51">
-        <v>3776.398287262131</v>
+        <v>3896.412046335423</v>
       </c>
       <c r="F51">
-        <v>5880.674194591285</v>
+        <v>6000.687953664577</v>
       </c>
       <c r="G51">
         <v>973</v>
@@ -5469,37 +5469,37 @@
         <v>623.1</v>
       </c>
       <c r="M51">
-        <v>697.4479594785265</v>
+        <v>711.6815913046189</v>
       </c>
       <c r="N51">
-        <v>-74.34795947852649</v>
+        <v>-88.58159130461888</v>
       </c>
       <c r="O51">
-        <v>-19.18177354545983</v>
+        <v>-22.85405055659167</v>
       </c>
       <c r="P51">
-        <v>-55.16618593306666</v>
+        <v>-65.72754074802721</v>
       </c>
       <c r="Q51">
-        <v>16.43381406693334</v>
+        <v>5.872459251972785</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1342214569569397</v>
+        <v>0.1359898860960785</v>
       </c>
       <c r="T51">
-        <v>2.042065980529785</v>
+        <v>2.082907300140381</v>
       </c>
       <c r="U51">
         <v>0.1186</v>
       </c>
       <c r="V51">
-        <v>0.2304971974112566</v>
+        <v>0.2258872534630314</v>
       </c>
       <c r="W51">
-        <v>0.09126303238702498</v>
+        <v>0.09180977173928448</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8933999899661108</v>
+        <v>0.8755319901667885</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1138998289176815</v>
+        <v>0.1146278289176815</v>
       </c>
       <c r="C52">
-        <v>2623.479300929075</v>
+        <v>2422.538250541595</v>
       </c>
       <c r="D52">
-        <v>7651.167254593652</v>
+        <v>7570.239963279464</v>
       </c>
       <c r="E52">
-        <v>3896.412046335423</v>
+        <v>4016.425805408715</v>
       </c>
       <c r="F52">
-        <v>6000.687953664577</v>
+        <v>6120.701712737869</v>
       </c>
       <c r="G52">
         <v>973</v>
@@ -5551,37 +5551,37 @@
         <v>623.1</v>
       </c>
       <c r="M52">
-        <v>711.6815913046189</v>
+        <v>725.9152231307114</v>
       </c>
       <c r="N52">
-        <v>-88.58159130461888</v>
+        <v>-102.8152231307114</v>
       </c>
       <c r="O52">
-        <v>-22.85405055659167</v>
+        <v>-26.52632756772354</v>
       </c>
       <c r="P52">
-        <v>-65.72754074802721</v>
+        <v>-76.28889556298785</v>
       </c>
       <c r="Q52">
-        <v>5.872459251972785</v>
+        <v>-4.688895562987852</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1359898860960785</v>
+        <v>0.1378304960164066</v>
       </c>
       <c r="T52">
-        <v>2.082907300140381</v>
+        <v>2.125415612388144</v>
       </c>
       <c r="U52">
         <v>0.1186</v>
       </c>
       <c r="V52">
-        <v>0.2258872534630314</v>
+        <v>0.221458091630423</v>
       </c>
       <c r="W52">
-        <v>0.09180977173928448</v>
+        <v>0.09233507033263184</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8755319901667885</v>
+        <v>0.8583646962419494</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1146278289176815</v>
+        <v>0.1153558289176815</v>
       </c>
       <c r="C53">
-        <v>2422.538250541595</v>
+        <v>2223.291236987364</v>
       </c>
       <c r="D53">
-        <v>7570.239963279464</v>
+        <v>7491.006708798524</v>
       </c>
       <c r="E53">
-        <v>4016.425805408715</v>
+        <v>4136.439564482006</v>
       </c>
       <c r="F53">
-        <v>6120.701712737869</v>
+        <v>6240.715471811161</v>
       </c>
       <c r="G53">
         <v>973</v>
@@ -5633,37 +5633,37 @@
         <v>623.1</v>
       </c>
       <c r="M53">
-        <v>725.9152231307114</v>
+        <v>740.1488549568037</v>
       </c>
       <c r="N53">
-        <v>-102.8152231307114</v>
+        <v>-117.0488549568037</v>
       </c>
       <c r="O53">
-        <v>-26.52632756772354</v>
+        <v>-30.19860457885535</v>
       </c>
       <c r="P53">
-        <v>-76.28889556298785</v>
+        <v>-86.85025037794833</v>
       </c>
       <c r="Q53">
-        <v>-4.688895562987852</v>
+        <v>-15.25025037794833</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1378304960164066</v>
+        <v>0.1397477980167484</v>
       </c>
       <c r="T53">
-        <v>2.125415612388144</v>
+        <v>2.169695104312897</v>
       </c>
       <c r="U53">
         <v>0.1186</v>
       </c>
       <c r="V53">
-        <v>0.221458091630423</v>
+        <v>0.2171992821759918</v>
       </c>
       <c r="W53">
-        <v>0.09233507033263184</v>
+        <v>0.09284016513392737</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8583646962419494</v>
+        <v>0.8418576828526813</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1153558289176815</v>
+        <v>0.1160838289176815</v>
       </c>
       <c r="C54">
-        <v>2223.291236987364</v>
+        <v>2025.685619758583</v>
       </c>
       <c r="D54">
-        <v>7491.006708798524</v>
+        <v>7413.414850643035</v>
       </c>
       <c r="E54">
-        <v>4136.439564482006</v>
+        <v>4256.453323555298</v>
       </c>
       <c r="F54">
-        <v>6240.715471811161</v>
+        <v>6360.729230884453</v>
       </c>
       <c r="G54">
         <v>973</v>
@@ -5715,37 +5715,37 @@
         <v>623.1</v>
       </c>
       <c r="M54">
-        <v>740.1488549568037</v>
+        <v>754.3824867828962</v>
       </c>
       <c r="N54">
-        <v>-117.0488549568037</v>
+        <v>-131.2824867828962</v>
       </c>
       <c r="O54">
-        <v>-30.19860457885535</v>
+        <v>-33.87088158998721</v>
       </c>
       <c r="P54">
-        <v>-86.85025037794833</v>
+        <v>-97.41160519290895</v>
       </c>
       <c r="Q54">
-        <v>-15.25025037794833</v>
+        <v>-25.81160519290896</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1397477980167484</v>
+        <v>0.1417466873362537</v>
       </c>
       <c r="T54">
-        <v>2.169695104312897</v>
+        <v>2.215858829936575</v>
       </c>
       <c r="U54">
         <v>0.1186</v>
       </c>
       <c r="V54">
-        <v>0.2171992821759918</v>
+        <v>0.2131011825122938</v>
       </c>
       <c r="W54">
-        <v>0.09284016513392737</v>
+        <v>0.09332619975404198</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8418576828526813</v>
+        <v>0.8259735756290456</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1160838289176815</v>
+        <v>0.1168118289176815</v>
       </c>
       <c r="C55">
-        <v>2025.685619758583</v>
+        <v>1829.670916990061</v>
       </c>
       <c r="D55">
-        <v>7413.414850643035</v>
+        <v>7337.413906947804</v>
       </c>
       <c r="E55">
-        <v>4256.453323555298</v>
+        <v>4376.467082628589</v>
       </c>
       <c r="F55">
-        <v>6360.729230884453</v>
+        <v>6480.742989957744</v>
       </c>
       <c r="G55">
         <v>973</v>
@@ -5797,37 +5797,37 @@
         <v>623.1</v>
       </c>
       <c r="M55">
-        <v>754.3824867828962</v>
+        <v>768.6161186089885</v>
       </c>
       <c r="N55">
-        <v>-131.2824867828962</v>
+        <v>-145.5161186089884</v>
       </c>
       <c r="O55">
-        <v>-33.87088158998721</v>
+        <v>-37.54315860111902</v>
       </c>
       <c r="P55">
-        <v>-97.41160519290895</v>
+        <v>-107.9729600078694</v>
       </c>
       <c r="Q55">
-        <v>-25.81160519290896</v>
+        <v>-36.37296000786944</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1417466873362537</v>
+        <v>0.1438324848870418</v>
       </c>
       <c r="T55">
-        <v>2.215858829936575</v>
+        <v>2.264029674065632</v>
       </c>
       <c r="U55">
         <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.2131011825122938</v>
+        <v>0.2091548643176217</v>
       </c>
       <c r="W55">
-        <v>0.09332619975404198</v>
+        <v>0.09379423309193007</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8259735756290456</v>
+        <v>0.8106777686729523</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1168118289176815</v>
+        <v>0.1651002542574064</v>
       </c>
       <c r="C56">
-        <v>1829.670916990061</v>
+        <v>-1260.262443996504</v>
       </c>
       <c r="D56">
-        <v>7337.413906947804</v>
+        <v>4367.494305034532</v>
       </c>
       <c r="E56">
-        <v>4376.467082628589</v>
+        <v>4496.480841701881</v>
       </c>
       <c r="F56">
-        <v>6480.742989957744</v>
+        <v>6600.756749031036</v>
       </c>
       <c r="G56">
         <v>973</v>
@@ -5879,45 +5879,45 @@
         <v>623.1</v>
       </c>
       <c r="M56">
-        <v>768.6161186089885</v>
+        <v>1325.431955205432</v>
       </c>
       <c r="N56">
-        <v>-145.5161186089884</v>
+        <v>-702.3319552054319</v>
       </c>
       <c r="O56">
-        <v>-37.54315860111902</v>
+        <v>-181.2016444430014</v>
       </c>
       <c r="P56">
-        <v>-107.9729600078694</v>
+        <v>-521.1303107624304</v>
       </c>
       <c r="Q56">
-        <v>-36.37296000786944</v>
+        <v>-449.5303107624304</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1438324848870418</v>
+        <v>0.1512341519728093</v>
       </c>
       <c r="T56">
-        <v>2.264029674065632</v>
+        <v>2.434968867732318</v>
       </c>
       <c r="U56">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.2091548643176217</v>
+        <v>0.1212886103799146</v>
       </c>
       <c r="W56">
-        <v>0.09379423309193007</v>
+        <v>0.1764452470357132</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8106777686729523</v>
+        <v>0.4701108929454053</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1651002542574064</v>
+        <v>0.1666502542574064</v>
       </c>
       <c r="C57">
-        <v>-1260.262443996504</v>
+        <v>-1436.292768482926</v>
       </c>
       <c r="D57">
-        <v>4367.494305034532</v>
+        <v>4311.477739621401</v>
       </c>
       <c r="E57">
-        <v>4496.480841701881</v>
+        <v>4616.494600775173</v>
       </c>
       <c r="F57">
-        <v>6600.756749031036</v>
+        <v>6720.770508104328</v>
       </c>
       <c r="G57">
         <v>973</v>
@@ -5961,37 +5961,37 @@
         <v>623.1</v>
       </c>
       <c r="M57">
-        <v>1325.431955205432</v>
+        <v>1349.530718027349</v>
       </c>
       <c r="N57">
-        <v>-702.3319552054319</v>
+        <v>-726.4307180273491</v>
       </c>
       <c r="O57">
-        <v>-181.2016444430014</v>
+        <v>-187.4191252510561</v>
       </c>
       <c r="P57">
-        <v>-521.1303107624304</v>
+        <v>-539.0115927762931</v>
       </c>
       <c r="Q57">
-        <v>-449.5303107624304</v>
+        <v>-467.4115927762931</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1512341519728093</v>
+        <v>0.1536303826994641</v>
       </c>
       <c r="T57">
-        <v>2.434968867732318</v>
+        <v>2.490309069271688</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1212886103799146</v>
+        <v>0.1191227423374161</v>
       </c>
       <c r="W57">
-        <v>0.1764452470357132</v>
+        <v>0.1768801533386469</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4701108929454053</v>
+        <v>0.4617160555713801</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1666502542574064</v>
+        <v>0.1682002542574064</v>
       </c>
       <c r="C58">
-        <v>-1436.292768482926</v>
+        <v>-1610.904375713945</v>
       </c>
       <c r="D58">
-        <v>4311.477739621401</v>
+        <v>4256.879891463674</v>
       </c>
       <c r="E58">
-        <v>4616.494600775173</v>
+        <v>4736.508359848464</v>
       </c>
       <c r="F58">
-        <v>6720.770508104328</v>
+        <v>6840.784267177619</v>
       </c>
       <c r="G58">
         <v>973</v>
@@ -6043,37 +6043,37 @@
         <v>623.1</v>
       </c>
       <c r="M58">
-        <v>1349.530718027349</v>
+        <v>1373.629480849266</v>
       </c>
       <c r="N58">
-        <v>-726.4307180273491</v>
+        <v>-750.529480849266</v>
       </c>
       <c r="O58">
-        <v>-187.4191252510561</v>
+        <v>-193.6366060591106</v>
       </c>
       <c r="P58">
-        <v>-539.0115927762931</v>
+        <v>-556.8928747901554</v>
       </c>
       <c r="Q58">
-        <v>-467.4115927762931</v>
+        <v>-485.2928747901553</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1536303826994641</v>
+        <v>0.1561380660180563</v>
       </c>
       <c r="T58">
-        <v>2.490309069271688</v>
+        <v>2.548223233673355</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1191227423374161</v>
+        <v>0.1170328696648298</v>
       </c>
       <c r="W58">
-        <v>0.1768801533386469</v>
+        <v>0.1772997997713022</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4617160555713801</v>
+        <v>0.4536157738946892</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1682002542574064</v>
+        <v>0.1697502542574064</v>
       </c>
       <c r="C59">
-        <v>-1610.904375713945</v>
+        <v>-1784.150488938496</v>
       </c>
       <c r="D59">
-        <v>4256.879891463674</v>
+        <v>4203.647537312415</v>
       </c>
       <c r="E59">
-        <v>4736.508359848464</v>
+        <v>4856.522118921756</v>
       </c>
       <c r="F59">
-        <v>6840.784267177619</v>
+        <v>6960.798026250911</v>
       </c>
       <c r="G59">
         <v>973</v>
@@ -6125,37 +6125,37 @@
         <v>623.1</v>
       </c>
       <c r="M59">
-        <v>1373.629480849266</v>
+        <v>1397.728243671183</v>
       </c>
       <c r="N59">
-        <v>-750.529480849266</v>
+        <v>-774.628243671183</v>
       </c>
       <c r="O59">
-        <v>-193.6366060591106</v>
+        <v>-199.8540868671652</v>
       </c>
       <c r="P59">
-        <v>-556.8928747901554</v>
+        <v>-574.7741568040178</v>
       </c>
       <c r="Q59">
-        <v>-485.2928747901553</v>
+        <v>-503.1741568040178</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1561380660180563</v>
+        <v>0.15876516282801</v>
       </c>
       <c r="T59">
-        <v>2.548223233673355</v>
+        <v>2.608895215427483</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1170328696648298</v>
+        <v>0.1150150615671603</v>
       </c>
       <c r="W59">
-        <v>0.1772997997713022</v>
+        <v>0.1777049756373142</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4536157738946892</v>
+        <v>0.4457948122758153</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1697502542574064</v>
+        <v>0.1713002542574064</v>
       </c>
       <c r="C60">
-        <v>-1784.150488938492</v>
+        <v>-1956.081702055108</v>
       </c>
       <c r="D60">
-        <v>4203.647537312417</v>
+        <v>4151.730083269093</v>
       </c>
       <c r="E60">
-        <v>4856.522118921755</v>
+        <v>4976.535877995047</v>
       </c>
       <c r="F60">
-        <v>6960.798026250909</v>
+        <v>7080.811785324201</v>
       </c>
       <c r="G60">
         <v>973</v>
@@ -6207,37 +6207,37 @@
         <v>623.1</v>
       </c>
       <c r="M60">
-        <v>1397.728243671183</v>
+        <v>1421.8270064931</v>
       </c>
       <c r="N60">
-        <v>-774.6282436711825</v>
+        <v>-798.7270064930996</v>
       </c>
       <c r="O60">
-        <v>-199.8540868671651</v>
+        <v>-206.0715676752197</v>
       </c>
       <c r="P60">
-        <v>-574.7741568040174</v>
+        <v>-592.6554388178799</v>
       </c>
       <c r="Q60">
-        <v>-503.1741568040173</v>
+        <v>-521.0554388178799</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.15876516282801</v>
+        <v>0.1615204107018638</v>
       </c>
       <c r="T60">
-        <v>2.608895215427483</v>
+        <v>2.672526806047665</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1150150615671604</v>
+        <v>0.1130656537439882</v>
       </c>
       <c r="W60">
-        <v>0.1777049756373142</v>
+        <v>0.1780964167282072</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4457948122758154</v>
+        <v>0.4382389679999541</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1713002542574064</v>
+        <v>0.1728502542574064</v>
       </c>
       <c r="C61">
-        <v>-1956.081702055108</v>
+        <v>-2126.746140000946</v>
       </c>
       <c r="D61">
-        <v>4151.730083269093</v>
+        <v>4101.079404396547</v>
       </c>
       <c r="E61">
-        <v>4976.535877995047</v>
+        <v>5096.549637068339</v>
       </c>
       <c r="F61">
-        <v>7080.811785324201</v>
+        <v>7200.825544397493</v>
       </c>
       <c r="G61">
         <v>973</v>
@@ -6289,37 +6289,37 @@
         <v>623.1</v>
       </c>
       <c r="M61">
-        <v>1421.8270064931</v>
+        <v>1445.925769315017</v>
       </c>
       <c r="N61">
-        <v>-798.7270064930996</v>
+        <v>-822.8257693150166</v>
       </c>
       <c r="O61">
-        <v>-206.0715676752197</v>
+        <v>-212.2890484832743</v>
       </c>
       <c r="P61">
-        <v>-592.6554388178799</v>
+        <v>-610.5367208317423</v>
       </c>
       <c r="Q61">
-        <v>-521.0554388178799</v>
+        <v>-538.9367208317423</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1615204107018638</v>
+        <v>0.1644134209694105</v>
       </c>
       <c r="T61">
-        <v>2.672526806047665</v>
+        <v>2.739339976198857</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1130656537439882</v>
+        <v>0.1111812261815884</v>
       </c>
       <c r="W61">
-        <v>0.1780964167282072</v>
+        <v>0.1784748097827371</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4382389679999541</v>
+        <v>0.4309349851999549</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1728502542574064</v>
+        <v>0.1744002542574064</v>
       </c>
       <c r="C62">
-        <v>-2126.746140000946</v>
+        <v>-2296.189607541928</v>
       </c>
       <c r="D62">
-        <v>4101.079404396547</v>
+        <v>4051.649695928856</v>
       </c>
       <c r="E62">
-        <v>5096.549637068339</v>
+        <v>5216.56339614163</v>
       </c>
       <c r="F62">
-        <v>7200.825544397493</v>
+        <v>7320.839303470784</v>
       </c>
       <c r="G62">
         <v>973</v>
@@ -6371,37 +6371,37 @@
         <v>623.1</v>
       </c>
       <c r="M62">
-        <v>1445.925769315017</v>
+        <v>1470.024532136933</v>
       </c>
       <c r="N62">
-        <v>-822.8257693150166</v>
+        <v>-846.9245321369334</v>
       </c>
       <c r="O62">
-        <v>-212.2890484832743</v>
+        <v>-218.5065292913288</v>
       </c>
       <c r="P62">
-        <v>-610.5367208317423</v>
+        <v>-628.4180028456046</v>
       </c>
       <c r="Q62">
-        <v>-538.9367208317423</v>
+        <v>-556.8180028456046</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1644134209694105</v>
+        <v>0.1674547907378569</v>
       </c>
       <c r="T62">
-        <v>2.739339976198857</v>
+        <v>2.809579462768059</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1111812261815884</v>
+        <v>0.1093585831294312</v>
       </c>
       <c r="W62">
-        <v>0.1784748097827371</v>
+        <v>0.1788407965076102</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4309349851999549</v>
+        <v>0.4238704772458572</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1744002542574064</v>
+        <v>0.1759502542574064</v>
       </c>
       <c r="C63">
-        <v>-2296.189607541928</v>
+        <v>-2464.455727430968</v>
       </c>
       <c r="D63">
-        <v>4051.649695928856</v>
+        <v>4003.397335113108</v>
       </c>
       <c r="E63">
-        <v>5216.56339614163</v>
+        <v>5336.577155214922</v>
       </c>
       <c r="F63">
-        <v>7320.839303470784</v>
+        <v>7440.853062544076</v>
       </c>
       <c r="G63">
         <v>973</v>
@@ -6453,37 +6453,37 @@
         <v>623.1</v>
       </c>
       <c r="M63">
-        <v>1470.024532136933</v>
+        <v>1494.12329495885</v>
       </c>
       <c r="N63">
-        <v>-846.9245321369334</v>
+        <v>-871.0232949588504</v>
       </c>
       <c r="O63">
-        <v>-218.5065292913288</v>
+        <v>-224.7240100993834</v>
       </c>
       <c r="P63">
-        <v>-628.4180028456046</v>
+        <v>-646.299284859467</v>
       </c>
       <c r="Q63">
-        <v>-556.8180028456046</v>
+        <v>-574.699284859467</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1674547907378569</v>
+        <v>0.1706562325993794</v>
       </c>
       <c r="T63">
-        <v>2.809579462768059</v>
+        <v>2.883515764419849</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1093585831294312</v>
+        <v>0.1075947350144403</v>
       </c>
       <c r="W63">
-        <v>0.1788407965076102</v>
+        <v>0.1791949772091004</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4238704772458572</v>
+        <v>0.4170338566451176</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1759502542574064</v>
+        <v>0.1775002542574064</v>
       </c>
       <c r="C64">
-        <v>-2464.455727430968</v>
+        <v>-2631.586068810147</v>
       </c>
       <c r="D64">
-        <v>4003.397335113108</v>
+        <v>3956.280752807221</v>
       </c>
       <c r="E64">
-        <v>5336.577155214922</v>
+        <v>5456.590914288213</v>
       </c>
       <c r="F64">
-        <v>7440.853062544076</v>
+        <v>7560.866821617367</v>
       </c>
       <c r="G64">
         <v>973</v>
@@ -6535,37 +6535,37 @@
         <v>623.1</v>
       </c>
       <c r="M64">
-        <v>1494.12329495885</v>
+        <v>1518.222057780767</v>
       </c>
       <c r="N64">
-        <v>-871.0232949588504</v>
+        <v>-895.1220577807675</v>
       </c>
       <c r="O64">
-        <v>-224.7240100993834</v>
+        <v>-230.941490907438</v>
       </c>
       <c r="P64">
-        <v>-646.299284859467</v>
+        <v>-664.1805668733294</v>
       </c>
       <c r="Q64">
-        <v>-574.699284859467</v>
+        <v>-592.5805668733294</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1706562325993794</v>
+        <v>0.1740307253723357</v>
       </c>
       <c r="T64">
-        <v>2.883515764419849</v>
+        <v>2.961448622917684</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1075947350144403</v>
+        <v>0.1058868820777032</v>
       </c>
       <c r="W64">
-        <v>0.1791949772091004</v>
+        <v>0.1795379140787972</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4170338566451176</v>
+        <v>0.4104142716190046</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1775002542574064</v>
+        <v>0.1790502542574064</v>
       </c>
       <c r="C65">
-        <v>-2631.586068810147</v>
+        <v>-2797.620266651273</v>
       </c>
       <c r="D65">
-        <v>3956.280752807221</v>
+        <v>3910.260314039387</v>
       </c>
       <c r="E65">
-        <v>5456.590914288213</v>
+        <v>5576.604673361505</v>
       </c>
       <c r="F65">
-        <v>7560.866821617367</v>
+        <v>7680.880580690659</v>
       </c>
       <c r="G65">
         <v>973</v>
@@ -6617,37 +6617,37 @@
         <v>623.1</v>
       </c>
       <c r="M65">
-        <v>1518.222057780767</v>
+        <v>1542.320820602685</v>
       </c>
       <c r="N65">
-        <v>-895.1220577807675</v>
+        <v>-919.2208206026845</v>
       </c>
       <c r="O65">
-        <v>-230.941490907438</v>
+        <v>-237.1589717154926</v>
       </c>
       <c r="P65">
-        <v>-664.1805668733294</v>
+        <v>-682.0618488871919</v>
       </c>
       <c r="Q65">
-        <v>-592.5805668733294</v>
+        <v>-610.4618488871919</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1740307253723357</v>
+        <v>0.1775926899660117</v>
       </c>
       <c r="T65">
-        <v>2.961448622917684</v>
+        <v>3.043711084665397</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1058868820777032</v>
+        <v>0.1042323995452391</v>
       </c>
       <c r="W65">
-        <v>0.1795379140787972</v>
+        <v>0.179870134171316</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4104142716190046</v>
+        <v>0.4040015486249576</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1790502542574064</v>
+        <v>0.1806002542574064</v>
       </c>
       <c r="C66">
-        <v>-2797.620266651273</v>
+        <v>-2962.596132956109</v>
       </c>
       <c r="D66">
-        <v>3910.260314039387</v>
+        <v>3865.298206807842</v>
       </c>
       <c r="E66">
-        <v>5576.604673361505</v>
+        <v>5696.618432434796</v>
       </c>
       <c r="F66">
-        <v>7680.880580690659</v>
+        <v>7800.89433976395</v>
       </c>
       <c r="G66">
         <v>973</v>
@@ -6699,37 +6699,37 @@
         <v>623.1</v>
       </c>
       <c r="M66">
-        <v>1542.320820602685</v>
+        <v>1566.419583424601</v>
       </c>
       <c r="N66">
-        <v>-919.2208206026845</v>
+        <v>-943.3195834246013</v>
       </c>
       <c r="O66">
-        <v>-237.1589717154926</v>
+        <v>-243.3764525235472</v>
       </c>
       <c r="P66">
-        <v>-682.0618488871919</v>
+        <v>-699.9431309010541</v>
       </c>
       <c r="Q66">
-        <v>-610.4618488871919</v>
+        <v>-628.3431309010541</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1775926899660117</v>
+        <v>0.181358195393612</v>
       </c>
       <c r="T66">
-        <v>3.043711084665397</v>
+        <v>3.130674258512979</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1042323995452391</v>
+        <v>0.10262882416762</v>
       </c>
       <c r="W66">
-        <v>0.179870134171316</v>
+        <v>0.1801921321071419</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4040015486249576</v>
+        <v>0.3977861401845737</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1806002542574064</v>
+        <v>0.1821502542574064</v>
       </c>
       <c r="C67">
-        <v>-2962.596132956109</v>
+        <v>-3126.549760372013</v>
       </c>
       <c r="D67">
-        <v>3865.298206807842</v>
+        <v>3821.358338465229</v>
       </c>
       <c r="E67">
-        <v>5696.618432434796</v>
+        <v>5816.632191508088</v>
       </c>
       <c r="F67">
-        <v>7800.89433976395</v>
+        <v>7920.908098837243</v>
       </c>
       <c r="G67">
         <v>973</v>
@@ -6781,37 +6781,37 @@
         <v>623.1</v>
       </c>
       <c r="M67">
-        <v>1566.419583424601</v>
+        <v>1590.518346246518</v>
       </c>
       <c r="N67">
-        <v>-943.3195834246013</v>
+        <v>-967.4183462465184</v>
       </c>
       <c r="O67">
-        <v>-243.3764525235472</v>
+        <v>-249.5939333316017</v>
       </c>
       <c r="P67">
-        <v>-699.9431309010541</v>
+        <v>-717.8244129149166</v>
       </c>
       <c r="Q67">
-        <v>-628.3431309010541</v>
+        <v>-646.2244129149166</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.181358195393612</v>
+        <v>0.1853452011404829</v>
       </c>
       <c r="T67">
-        <v>3.130674258512979</v>
+        <v>3.222752913175126</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.10262882416762</v>
+        <v>0.1010738419832621</v>
       </c>
       <c r="W67">
-        <v>0.1801921321071419</v>
+        <v>0.180504372529761</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3977861401845737</v>
+        <v>0.3917590774545043</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1821502542574064</v>
+        <v>0.1837002542574064</v>
       </c>
       <c r="C68">
-        <v>-3126.549760372013</v>
+        <v>-3289.515618819719</v>
       </c>
       <c r="D68">
-        <v>3821.358338465229</v>
+        <v>3778.406239090816</v>
       </c>
       <c r="E68">
-        <v>5816.632191508088</v>
+        <v>5936.64595058138</v>
       </c>
       <c r="F68">
-        <v>7920.908098837243</v>
+        <v>8040.921857910535</v>
       </c>
       <c r="G68">
         <v>973</v>
@@ -6863,37 +6863,37 @@
         <v>623.1</v>
       </c>
       <c r="M68">
-        <v>1590.518346246518</v>
+        <v>1614.617109068435</v>
       </c>
       <c r="N68">
-        <v>-967.4183462465184</v>
+        <v>-991.5171090684354</v>
       </c>
       <c r="O68">
-        <v>-249.5939333316017</v>
+        <v>-255.8114141396563</v>
       </c>
       <c r="P68">
-        <v>-717.8244129149166</v>
+        <v>-735.7056949287791</v>
       </c>
       <c r="Q68">
-        <v>-646.2244129149166</v>
+        <v>-664.105694928779</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1853452011404829</v>
+        <v>0.1895738435992855</v>
       </c>
       <c r="T68">
-        <v>3.222752913175126</v>
+        <v>3.320412092362251</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1010738419832621</v>
+        <v>0.09956527717754179</v>
       </c>
       <c r="W68">
-        <v>0.180504372529761</v>
+        <v>0.1808072923427496</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3917590774545043</v>
+        <v>0.3859119270447356</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1837002542574064</v>
+        <v>0.1852502542574064</v>
       </c>
       <c r="C69">
-        <v>-3289.515618819719</v>
+        <v>-3451.526645676978</v>
       </c>
       <c r="D69">
-        <v>3778.406239090816</v>
+        <v>3736.408971306847</v>
       </c>
       <c r="E69">
-        <v>5936.64595058138</v>
+        <v>6056.659709654671</v>
       </c>
       <c r="F69">
-        <v>8040.921857910535</v>
+        <v>8160.935616983826</v>
       </c>
       <c r="G69">
         <v>973</v>
@@ -6945,37 +6945,37 @@
         <v>623.1</v>
       </c>
       <c r="M69">
-        <v>1614.617109068435</v>
+        <v>1638.715871890352</v>
       </c>
       <c r="N69">
-        <v>-991.5171090684354</v>
+        <v>-1015.615871890352</v>
       </c>
       <c r="O69">
-        <v>-255.8114141396563</v>
+        <v>-262.0288949477109</v>
       </c>
       <c r="P69">
-        <v>-735.7056949287791</v>
+        <v>-753.5869769426413</v>
       </c>
       <c r="Q69">
-        <v>-664.105694928779</v>
+        <v>-681.9869769426413</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1895738435992855</v>
+        <v>0.1940667762117631</v>
       </c>
       <c r="T69">
-        <v>3.320412092362251</v>
+        <v>3.424174970248572</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.09956527717754179</v>
+        <v>0.0981010819249309</v>
       </c>
       <c r="W69">
-        <v>0.1808072923427496</v>
+        <v>0.1811013027494739</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3859119270447356</v>
+        <v>0.380236751647019</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1852502542574064</v>
+        <v>0.1868002542574065</v>
       </c>
       <c r="C70">
-        <v>-3451.526645676978</v>
+        <v>-3612.61433001393</v>
       </c>
       <c r="D70">
-        <v>3736.408971306847</v>
+        <v>3695.335046043187</v>
       </c>
       <c r="E70">
-        <v>6056.659709654671</v>
+        <v>6176.673468727962</v>
       </c>
       <c r="F70">
-        <v>8160.935616983826</v>
+        <v>8280.949376057117</v>
       </c>
       <c r="G70">
         <v>973</v>
@@ -7027,37 +7027,37 @@
         <v>623.1</v>
       </c>
       <c r="M70">
-        <v>1638.715871890352</v>
+        <v>1662.814634712269</v>
       </c>
       <c r="N70">
-        <v>-1015.615871890352</v>
+        <v>-1039.714634712269</v>
       </c>
       <c r="O70">
-        <v>-262.0288949477109</v>
+        <v>-268.2463757557654</v>
       </c>
       <c r="P70">
-        <v>-753.5869769426413</v>
+        <v>-771.4682589565035</v>
       </c>
       <c r="Q70">
-        <v>-681.9869769426413</v>
+        <v>-699.8682589565035</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1940667762117631</v>
+        <v>0.1988495754444007</v>
       </c>
       <c r="T70">
-        <v>3.424174970248572</v>
+        <v>3.534632227353365</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.0981010819249309</v>
+        <v>0.09667932711442466</v>
       </c>
       <c r="W70">
-        <v>0.1811013027494739</v>
+        <v>0.1813867911154236</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.380236751647019</v>
+        <v>0.3747260740869174</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1868002542574065</v>
+        <v>0.1883502542574065</v>
       </c>
       <c r="C71">
-        <v>-3612.61433001393</v>
+        <v>-3772.80879133293</v>
       </c>
       <c r="D71">
-        <v>3695.335046043187</v>
+        <v>3655.154343797479</v>
       </c>
       <c r="E71">
-        <v>6176.673468727962</v>
+        <v>6296.687227801254</v>
       </c>
       <c r="F71">
-        <v>8280.949376057117</v>
+        <v>8400.963135130409</v>
       </c>
       <c r="G71">
         <v>973</v>
@@ -7109,37 +7109,37 @@
         <v>623.1</v>
       </c>
       <c r="M71">
-        <v>1662.814634712269</v>
+        <v>1686.913397534186</v>
       </c>
       <c r="N71">
-        <v>-1039.714634712269</v>
+        <v>-1063.813397534186</v>
       </c>
       <c r="O71">
-        <v>-268.2463757557654</v>
+        <v>-274.4638565638201</v>
       </c>
       <c r="P71">
-        <v>-771.4682589565035</v>
+        <v>-789.3495409703661</v>
       </c>
       <c r="Q71">
-        <v>-699.8682589565035</v>
+        <v>-717.7495409703661</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1988495754444007</v>
+        <v>0.203951227959214</v>
       </c>
       <c r="T71">
-        <v>3.534632227353365</v>
+        <v>3.652453301598477</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.09667932711442466</v>
+        <v>0.09529819386993288</v>
       </c>
       <c r="W71">
-        <v>0.1813867911154236</v>
+        <v>0.1816641226709175</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3747260740869174</v>
+        <v>0.3693728444571041</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1883502542574065</v>
+        <v>0.1899002542574065</v>
       </c>
       <c r="C72">
-        <v>-3772.80879133293</v>
+        <v>-3932.138853226659</v>
       </c>
       <c r="D72">
-        <v>3655.154343797479</v>
+        <v>3615.838040977042</v>
       </c>
       <c r="E72">
-        <v>6296.687227801254</v>
+        <v>6416.700986874546</v>
       </c>
       <c r="F72">
-        <v>8400.963135130409</v>
+        <v>8520.976894203701</v>
       </c>
       <c r="G72">
         <v>973</v>
@@ -7191,37 +7191,37 @@
         <v>623.1</v>
       </c>
       <c r="M72">
-        <v>1686.913397534186</v>
+        <v>1711.012160356103</v>
       </c>
       <c r="N72">
-        <v>-1063.813397534186</v>
+        <v>-1087.912160356103</v>
       </c>
       <c r="O72">
-        <v>-274.4638565638201</v>
+        <v>-280.6813373718746</v>
       </c>
       <c r="P72">
-        <v>-789.3495409703661</v>
+        <v>-807.2308229842283</v>
       </c>
       <c r="Q72">
-        <v>-717.7495409703661</v>
+        <v>-735.6308229842283</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.203951227959214</v>
+        <v>0.2094047185784973</v>
       </c>
       <c r="T72">
-        <v>3.652453301598477</v>
+        <v>3.778399967170839</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.09529819386993288</v>
+        <v>0.09395596578725776</v>
       </c>
       <c r="W72">
-        <v>0.1816641226709175</v>
+        <v>0.1819336420699187</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3693728444571041</v>
+        <v>0.3641704100281309</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1899002542574064</v>
+        <v>0.1914502542574064</v>
       </c>
       <c r="C73">
-        <v>-3932.138853226656</v>
+        <v>-4090.632112333016</v>
       </c>
       <c r="D73">
-        <v>3615.838040977043</v>
+        <v>3577.358540943974</v>
       </c>
       <c r="E73">
-        <v>6416.700986874544</v>
+        <v>6536.714745947836</v>
       </c>
       <c r="F73">
-        <v>8520.976894203699</v>
+        <v>8640.990653276991</v>
       </c>
       <c r="G73">
         <v>973</v>
@@ -7273,37 +7273,37 @@
         <v>623.1</v>
       </c>
       <c r="M73">
-        <v>1711.012160356103</v>
+        <v>1735.11092317802</v>
       </c>
       <c r="N73">
-        <v>-1087.912160356103</v>
+        <v>-1112.01092317802</v>
       </c>
       <c r="O73">
-        <v>-280.6813373718746</v>
+        <v>-286.8988181799291</v>
       </c>
       <c r="P73">
-        <v>-807.2308229842283</v>
+        <v>-825.1121049980907</v>
       </c>
       <c r="Q73">
-        <v>-735.6308229842283</v>
+        <v>-753.5121049980906</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2094047185784972</v>
+        <v>0.215247744242015</v>
       </c>
       <c r="T73">
-        <v>3.778399967170837</v>
+        <v>3.913342823141224</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.09395596578725778</v>
+        <v>0.0926510218179903</v>
       </c>
       <c r="W73">
-        <v>0.1819336420699187</v>
+        <v>0.1821956748189476</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3641704100281308</v>
+        <v>0.3591124876666291</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1914502542574064</v>
+        <v>0.1930002542574064</v>
       </c>
       <c r="C74">
-        <v>-4090.632112333016</v>
+        <v>-4248.315002933533</v>
       </c>
       <c r="D74">
-        <v>3577.358540943974</v>
+        <v>3539.68940941675</v>
       </c>
       <c r="E74">
-        <v>6536.714745947836</v>
+        <v>6656.728505021129</v>
       </c>
       <c r="F74">
-        <v>8640.990653276991</v>
+        <v>8761.004412350283</v>
       </c>
       <c r="G74">
         <v>973</v>
@@ -7355,37 +7355,37 @@
         <v>623.1</v>
       </c>
       <c r="M74">
-        <v>1735.11092317802</v>
+        <v>1759.209685999937</v>
       </c>
       <c r="N74">
-        <v>-1112.01092317802</v>
+        <v>-1136.109685999937</v>
       </c>
       <c r="O74">
-        <v>-286.8988181799291</v>
+        <v>-293.1162989879838</v>
       </c>
       <c r="P74">
-        <v>-825.1121049980907</v>
+        <v>-842.9933870119532</v>
       </c>
       <c r="Q74">
-        <v>-753.5121049980906</v>
+        <v>-771.3933870119532</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.215247744242015</v>
+        <v>0.2215235866213488</v>
       </c>
       <c r="T74">
-        <v>3.913342823141224</v>
+        <v>4.058281446220528</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.0926510218179903</v>
+        <v>0.0913818297382918</v>
       </c>
       <c r="W74">
-        <v>0.1821956748189476</v>
+        <v>0.182450528588551</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3591124876666291</v>
+        <v>0.3541931385205107</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1930002542574064</v>
+        <v>0.1945502542574064</v>
       </c>
       <c r="C75">
-        <v>-4248.315002933533</v>
+        <v>-4405.212857512987</v>
       </c>
       <c r="D75">
-        <v>3539.68940941675</v>
+        <v>3502.805313910588</v>
       </c>
       <c r="E75">
-        <v>6656.728505021129</v>
+        <v>6776.742264094421</v>
       </c>
       <c r="F75">
-        <v>8761.004412350283</v>
+        <v>8881.018171423575</v>
       </c>
       <c r="G75">
         <v>973</v>
@@ -7437,37 +7437,37 @@
         <v>623.1</v>
       </c>
       <c r="M75">
-        <v>1759.209685999937</v>
+        <v>1783.308448821854</v>
       </c>
       <c r="N75">
-        <v>-1136.109685999937</v>
+        <v>-1160.208448821854</v>
       </c>
       <c r="O75">
-        <v>-293.1162989879838</v>
+        <v>-299.3337797960383</v>
       </c>
       <c r="P75">
-        <v>-842.9933870119532</v>
+        <v>-860.8746690258156</v>
       </c>
       <c r="Q75">
-        <v>-771.3933870119532</v>
+        <v>-789.2746690258156</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2215235866213488</v>
+        <v>0.2282821861067854</v>
       </c>
       <c r="T75">
-        <v>4.058281446220528</v>
+        <v>4.214369194152088</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.0913818297382918</v>
+        <v>0.09014694014723379</v>
       </c>
       <c r="W75">
-        <v>0.182450528588551</v>
+        <v>0.1826984944184355</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3541931385205107</v>
+        <v>0.3494067447567202</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1945502542574064</v>
+        <v>0.1961002542574064</v>
       </c>
       <c r="C76">
-        <v>-4405.212857512987</v>
+        <v>-4561.349963571859</v>
       </c>
       <c r="D76">
-        <v>3502.805313910588</v>
+        <v>3466.681966925006</v>
       </c>
       <c r="E76">
-        <v>6776.742264094421</v>
+        <v>6896.756023167711</v>
       </c>
       <c r="F76">
-        <v>8881.018171423575</v>
+        <v>9001.031930496865</v>
       </c>
       <c r="G76">
         <v>973</v>
@@ -7519,37 +7519,37 @@
         <v>623.1</v>
       </c>
       <c r="M76">
-        <v>1783.308448821854</v>
+        <v>1807.407211643771</v>
       </c>
       <c r="N76">
-        <v>-1160.208448821854</v>
+        <v>-1184.307211643771</v>
       </c>
       <c r="O76">
-        <v>-299.3337797960383</v>
+        <v>-305.5512606040928</v>
       </c>
       <c r="P76">
-        <v>-860.8746690258156</v>
+        <v>-878.7559510396778</v>
       </c>
       <c r="Q76">
-        <v>-789.2746690258156</v>
+        <v>-807.1559510396778</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2282821861067854</v>
+        <v>0.2355814735510568</v>
       </c>
       <c r="T76">
-        <v>4.214369194152088</v>
+        <v>4.382943961918171</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.09014694014723379</v>
+        <v>0.0889449809452707</v>
       </c>
       <c r="W76">
-        <v>0.1826984944184355</v>
+        <v>0.1829398478261897</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3494067447567202</v>
+        <v>0.3447479881599639</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1961002542574064</v>
+        <v>0.1976502542574065</v>
       </c>
       <c r="C77">
-        <v>-4561.349963571859</v>
+        <v>-4716.749616959331</v>
       </c>
       <c r="D77">
-        <v>3466.681966925006</v>
+        <v>3431.296072610827</v>
       </c>
       <c r="E77">
-        <v>6896.756023167711</v>
+        <v>7016.769782241003</v>
       </c>
       <c r="F77">
-        <v>9001.031930496865</v>
+        <v>9121.045689570157</v>
       </c>
       <c r="G77">
         <v>973</v>
@@ -7601,37 +7601,37 @@
         <v>623.1</v>
       </c>
       <c r="M77">
-        <v>1807.407211643771</v>
+        <v>1831.505974465688</v>
       </c>
       <c r="N77">
-        <v>-1184.307211643771</v>
+        <v>-1208.405974465687</v>
       </c>
       <c r="O77">
-        <v>-305.5512606040928</v>
+        <v>-311.7687414121474</v>
       </c>
       <c r="P77">
-        <v>-878.7559510396778</v>
+        <v>-896.6372330535401</v>
       </c>
       <c r="Q77">
-        <v>-807.1559510396778</v>
+        <v>-825.03723305354</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2355814735510568</v>
+        <v>0.2434890349490175</v>
       </c>
       <c r="T77">
-        <v>4.382943961918171</v>
+        <v>4.565566626998096</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.0889449809452707</v>
+        <v>0.08777465224862238</v>
       </c>
       <c r="W77">
-        <v>0.1829398478261897</v>
+        <v>0.1831748498284766</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3447479881599639</v>
+        <v>0.3402118304210171</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1976502542574065</v>
+        <v>0.1992002542574064</v>
       </c>
       <c r="C78">
-        <v>-4716.749616959331</v>
+        <v>-4871.434171972909</v>
       </c>
       <c r="D78">
-        <v>3431.296072610827</v>
+        <v>3396.62527667054</v>
       </c>
       <c r="E78">
-        <v>7016.769782241003</v>
+        <v>7136.783541314295</v>
       </c>
       <c r="F78">
-        <v>9121.045689570157</v>
+        <v>9241.059448643449</v>
       </c>
       <c r="G78">
         <v>973</v>
@@ -7683,37 +7683,37 @@
         <v>623.1</v>
       </c>
       <c r="M78">
-        <v>1831.505974465688</v>
+        <v>1855.604737287605</v>
       </c>
       <c r="N78">
-        <v>-1208.405974465687</v>
+        <v>-1232.504737287605</v>
       </c>
       <c r="O78">
-        <v>-311.7687414121474</v>
+        <v>-317.986222220202</v>
       </c>
       <c r="P78">
-        <v>-896.6372330535401</v>
+        <v>-914.5185150674026</v>
       </c>
       <c r="Q78">
-        <v>-825.03723305354</v>
+        <v>-842.9185150674026</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2434890349490175</v>
+        <v>0.2520842103815835</v>
       </c>
       <c r="T78">
-        <v>4.565566626998096</v>
+        <v>4.7640695238241</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.08777465224862238</v>
+        <v>0.08663472169993898</v>
       </c>
       <c r="W78">
-        <v>0.1831748498284766</v>
+        <v>0.1834037478826523</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3402118304210171</v>
+        <v>0.3357934949610037</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1992002542574064</v>
+        <v>0.2007502542574064</v>
       </c>
       <c r="C79">
-        <v>-4871.434171972909</v>
+        <v>-5025.425088451142</v>
       </c>
       <c r="D79">
-        <v>3396.62527667054</v>
+        <v>3362.648119265599</v>
       </c>
       <c r="E79">
-        <v>7136.783541314295</v>
+        <v>7256.797300387587</v>
       </c>
       <c r="F79">
-        <v>9241.059448643449</v>
+        <v>9361.073207716741</v>
       </c>
       <c r="G79">
         <v>973</v>
@@ -7765,37 +7765,37 @@
         <v>623.1</v>
       </c>
       <c r="M79">
-        <v>1855.604737287605</v>
+        <v>1879.703500109522</v>
       </c>
       <c r="N79">
-        <v>-1232.504737287605</v>
+        <v>-1256.603500109522</v>
       </c>
       <c r="O79">
-        <v>-317.986222220202</v>
+        <v>-324.2037030282565</v>
       </c>
       <c r="P79">
-        <v>-914.5185150674026</v>
+        <v>-932.399797081265</v>
       </c>
       <c r="Q79">
-        <v>-842.9185150674026</v>
+        <v>-860.799797081265</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2520842103815835</v>
+        <v>0.2614607653989282</v>
       </c>
       <c r="T79">
-        <v>4.7640695238241</v>
+        <v>4.980618138543377</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.08663472169993898</v>
+        <v>0.08552402013968334</v>
       </c>
       <c r="W79">
-        <v>0.1834037478826523</v>
+        <v>0.1836267767559516</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3357934949610037</v>
+        <v>0.3314884501538115</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2007502542574064</v>
+        <v>0.2023002542574064</v>
       </c>
       <c r="C80">
-        <v>-5025.425088451142</v>
+        <v>-5178.742976067822</v>
       </c>
       <c r="D80">
-        <v>3362.648119265599</v>
+        <v>3329.343990722211</v>
       </c>
       <c r="E80">
-        <v>7256.797300387587</v>
+        <v>7376.811059460879</v>
       </c>
       <c r="F80">
-        <v>9361.073207716741</v>
+        <v>9481.086966790033</v>
       </c>
       <c r="G80">
         <v>973</v>
@@ -7847,37 +7847,37 @@
         <v>623.1</v>
       </c>
       <c r="M80">
-        <v>1879.703500109522</v>
+        <v>1903.802262931439</v>
       </c>
       <c r="N80">
-        <v>-1256.603500109522</v>
+        <v>-1280.702262931439</v>
       </c>
       <c r="O80">
-        <v>-324.2037030282565</v>
+        <v>-330.4211838363112</v>
       </c>
       <c r="P80">
-        <v>-932.399797081265</v>
+        <v>-950.2810790951276</v>
       </c>
       <c r="Q80">
-        <v>-860.799797081265</v>
+        <v>-878.6810790951275</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2614607653989282</v>
+        <v>0.27173032565602</v>
       </c>
       <c r="T80">
-        <v>4.980618138543377</v>
+        <v>5.217790430854967</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.08552402013968334</v>
+        <v>0.08444143760626963</v>
       </c>
       <c r="W80">
-        <v>0.1836267767559516</v>
+        <v>0.183844159328661</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3314884501538115</v>
+        <v>0.3272923938227504</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2023002542574064</v>
+        <v>0.2038502542574064</v>
       </c>
       <c r="C81">
-        <v>-5178.742976067822</v>
+        <v>-5331.40763601986</v>
       </c>
       <c r="D81">
-        <v>3329.343990722211</v>
+        <v>3296.693089843464</v>
       </c>
       <c r="E81">
-        <v>7376.811059460879</v>
+        <v>7496.824818534169</v>
       </c>
       <c r="F81">
-        <v>9481.086966790033</v>
+        <v>9601.100725863324</v>
       </c>
       <c r="G81">
         <v>973</v>
@@ -7929,37 +7929,37 @@
         <v>623.1</v>
       </c>
       <c r="M81">
-        <v>1903.802262931439</v>
+        <v>1927.901025753355</v>
       </c>
       <c r="N81">
-        <v>-1280.702262931439</v>
+        <v>-1304.801025753356</v>
       </c>
       <c r="O81">
-        <v>-330.4211838363112</v>
+        <v>-336.6386646443657</v>
       </c>
       <c r="P81">
-        <v>-950.2810790951276</v>
+        <v>-968.1623611089899</v>
       </c>
       <c r="Q81">
-        <v>-878.6810790951275</v>
+        <v>-896.5623611089899</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.27173032565602</v>
+        <v>0.283026841938821</v>
       </c>
       <c r="T81">
-        <v>5.217790430854967</v>
+        <v>5.478679952397715</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.08444143760626963</v>
+        <v>0.08338591963619127</v>
       </c>
       <c r="W81">
-        <v>0.183844159328661</v>
+        <v>0.1840561073370528</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3272923938227504</v>
+        <v>0.3232012388999661</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2038502542574064</v>
+        <v>0.2054002542574064</v>
       </c>
       <c r="C82">
-        <v>-5331.40763601986</v>
+        <v>-5483.438100285965</v>
       </c>
       <c r="D82">
-        <v>3296.693089843464</v>
+        <v>3264.676384650651</v>
       </c>
       <c r="E82">
-        <v>7496.824818534169</v>
+        <v>7616.838577607461</v>
       </c>
       <c r="F82">
-        <v>9601.100725863324</v>
+        <v>9721.114484936616</v>
       </c>
       <c r="G82">
         <v>973</v>
@@ -8011,37 +8011,37 @@
         <v>623.1</v>
       </c>
       <c r="M82">
-        <v>1927.901025753355</v>
+        <v>1951.999788575273</v>
       </c>
       <c r="N82">
-        <v>-1304.801025753356</v>
+        <v>-1328.899788575272</v>
       </c>
       <c r="O82">
-        <v>-336.6386646443657</v>
+        <v>-342.8561454524203</v>
       </c>
       <c r="P82">
-        <v>-968.1623611089899</v>
+        <v>-986.0436431228521</v>
       </c>
       <c r="Q82">
-        <v>-896.5623611089899</v>
+        <v>-914.4436431228521</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.283026841938821</v>
+        <v>0.295512465198759</v>
       </c>
       <c r="T82">
-        <v>5.478679952397715</v>
+        <v>5.7670315288397</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.08338591963619127</v>
+        <v>0.0823564638382136</v>
       </c>
       <c r="W82">
-        <v>0.1840561073370528</v>
+        <v>0.1842628220612867</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3232012388999661</v>
+        <v>0.3192111001481147</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2054002542574064</v>
+        <v>0.2069502542574064</v>
       </c>
       <c r="C83">
-        <v>-5483.438100285965</v>
+        <v>-5634.852668619698</v>
       </c>
       <c r="D83">
-        <v>3264.676384650651</v>
+        <v>3233.275575390209</v>
       </c>
       <c r="E83">
-        <v>7616.838577607461</v>
+        <v>7736.852336680753</v>
       </c>
       <c r="F83">
-        <v>9721.114484936616</v>
+        <v>9841.128244009908</v>
       </c>
       <c r="G83">
         <v>973</v>
@@ -8093,37 +8093,37 @@
         <v>623.1</v>
       </c>
       <c r="M83">
-        <v>1951.999788575273</v>
+        <v>1976.09855139719</v>
       </c>
       <c r="N83">
-        <v>-1328.899788575272</v>
+        <v>-1352.99855139719</v>
       </c>
       <c r="O83">
-        <v>-342.8561454524203</v>
+        <v>-349.073626260475</v>
       </c>
       <c r="P83">
-        <v>-986.0436431228521</v>
+        <v>-1003.924925136715</v>
       </c>
       <c r="Q83">
-        <v>-914.4436431228521</v>
+        <v>-932.3249251367147</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.295512465198759</v>
+        <v>0.3093853799320234</v>
       </c>
       <c r="T83">
-        <v>5.7670315288397</v>
+        <v>6.087422169330795</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.0823564638382136</v>
+        <v>0.08135211671823538</v>
       </c>
       <c r="W83">
-        <v>0.1842628220612867</v>
+        <v>0.1844644949629783</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3192111001481147</v>
+        <v>0.3153182818536254</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2069502542574064</v>
+        <v>0.2085002542574065</v>
       </c>
       <c r="C84">
-        <v>-5634.852668619698</v>
+        <v>-5785.668943428007</v>
       </c>
       <c r="D84">
-        <v>3233.275575390209</v>
+        <v>3202.473059655192</v>
       </c>
       <c r="E84">
-        <v>7736.852336680753</v>
+        <v>7856.866095754045</v>
       </c>
       <c r="F84">
-        <v>9841.128244009908</v>
+        <v>9961.1420030832</v>
       </c>
       <c r="G84">
         <v>973</v>
@@ -8175,37 +8175,37 @@
         <v>623.1</v>
       </c>
       <c r="M84">
-        <v>1976.09855139719</v>
+        <v>2000.197314219107</v>
       </c>
       <c r="N84">
-        <v>-1352.99855139719</v>
+        <v>-1377.097314219106</v>
       </c>
       <c r="O84">
-        <v>-349.073626260475</v>
+        <v>-355.2911070685295</v>
       </c>
       <c r="P84">
-        <v>-1003.924925136715</v>
+        <v>-1021.806207150577</v>
       </c>
       <c r="Q84">
-        <v>-932.3249251367147</v>
+        <v>-950.2062071505769</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3093853799320234</v>
+        <v>0.324890402280966</v>
       </c>
       <c r="T84">
-        <v>6.087422169330795</v>
+        <v>6.445505826350255</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.08135211671823538</v>
+        <v>0.08037197073367831</v>
       </c>
       <c r="W84">
-        <v>0.1844644949629783</v>
+        <v>0.1846613082766774</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3153182818536254</v>
+        <v>0.3115192664096059</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2085002542574065</v>
+        <v>0.2100502542574064</v>
       </c>
       <c r="C85">
-        <v>-5785.668943428007</v>
+        <v>-5935.903862674886</v>
       </c>
       <c r="D85">
-        <v>3202.473059655192</v>
+        <v>3172.251899481606</v>
       </c>
       <c r="E85">
-        <v>7856.866095754045</v>
+        <v>7976.879854827337</v>
       </c>
       <c r="F85">
-        <v>9961.1420030832</v>
+        <v>10081.15576215649</v>
       </c>
       <c r="G85">
         <v>973</v>
@@ -8257,37 +8257,37 @@
         <v>623.1</v>
       </c>
       <c r="M85">
-        <v>2000.197314219107</v>
+        <v>2024.296077041024</v>
       </c>
       <c r="N85">
-        <v>-1377.097314219106</v>
+        <v>-1401.196077041024</v>
       </c>
       <c r="O85">
-        <v>-355.2911070685295</v>
+        <v>-361.5085878765842</v>
       </c>
       <c r="P85">
-        <v>-1021.806207150577</v>
+        <v>-1039.68748916444</v>
       </c>
       <c r="Q85">
-        <v>-950.2062071505769</v>
+        <v>-968.0874891644395</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.324890402280966</v>
+        <v>0.3423335524235264</v>
       </c>
       <c r="T85">
-        <v>6.445505826350255</v>
+        <v>6.848349940497146</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.08037197073367831</v>
+        <v>0.07941516155827738</v>
       </c>
       <c r="W85">
-        <v>0.1846613082766774</v>
+        <v>0.1848534355590979</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3115192664096059</v>
+        <v>0.3078107037142533</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2100502542574064</v>
+        <v>0.2116002542574065</v>
       </c>
       <c r="C86">
-        <v>-5935.903862674884</v>
+        <v>-6085.573730939437</v>
       </c>
       <c r="D86">
-        <v>3172.251899481606</v>
+        <v>3142.595790290344</v>
       </c>
       <c r="E86">
-        <v>7976.879854827335</v>
+        <v>8096.893613900627</v>
       </c>
       <c r="F86">
-        <v>10081.15576215649</v>
+        <v>10201.16952122978</v>
       </c>
       <c r="G86">
         <v>973</v>
@@ -8339,37 +8339,37 @@
         <v>623.1</v>
       </c>
       <c r="M86">
-        <v>2024.296077041023</v>
+        <v>2048.39483986294</v>
       </c>
       <c r="N86">
-        <v>-1401.196077041023</v>
+        <v>-1425.294839862941</v>
       </c>
       <c r="O86">
-        <v>-361.508587876584</v>
+        <v>-367.7260686846387</v>
       </c>
       <c r="P86">
-        <v>-1039.687489164439</v>
+        <v>-1057.568771178302</v>
       </c>
       <c r="Q86">
-        <v>-968.0874891644393</v>
+        <v>-985.9687711783018</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3423335524235261</v>
+        <v>0.3621024559184279</v>
       </c>
       <c r="T86">
-        <v>6.848349940497141</v>
+        <v>7.304906603196952</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.07941516155827739</v>
+        <v>0.07848086553994472</v>
       </c>
       <c r="W86">
-        <v>0.1848534355590979</v>
+        <v>0.1850410421995791</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3078107037142535</v>
+        <v>0.3041894013176151</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2116002542574065</v>
+        <v>0.2131502542574064</v>
       </c>
       <c r="C87">
-        <v>-6085.573730939437</v>
+        <v>-6234.694248747961</v>
       </c>
       <c r="D87">
-        <v>3142.595790290344</v>
+        <v>3113.489031555113</v>
       </c>
       <c r="E87">
-        <v>8096.893613900627</v>
+        <v>8216.907372973919</v>
       </c>
       <c r="F87">
-        <v>10201.16952122978</v>
+        <v>10321.18328030307</v>
       </c>
       <c r="G87">
         <v>973</v>
@@ -8421,37 +8421,37 @@
         <v>623.1</v>
       </c>
       <c r="M87">
-        <v>2048.39483986294</v>
+        <v>2072.493602684857</v>
       </c>
       <c r="N87">
-        <v>-1425.294839862941</v>
+        <v>-1449.393602684857</v>
       </c>
       <c r="O87">
-        <v>-367.7260686846387</v>
+        <v>-373.9435494926932</v>
       </c>
       <c r="P87">
-        <v>-1057.568771178302</v>
+        <v>-1075.450053192164</v>
       </c>
       <c r="Q87">
-        <v>-985.9687711783018</v>
+        <v>-1003.850053192164</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3621024559184279</v>
+        <v>0.3846954884840299</v>
       </c>
       <c r="T87">
-        <v>7.304906603196952</v>
+        <v>7.826685646282447</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.07848086553994472</v>
+        <v>0.07756829733599188</v>
       </c>
       <c r="W87">
-        <v>0.1850410421995791</v>
+        <v>0.1852242858949328</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3041894013176151</v>
+        <v>0.3006523152557824</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2131502542574064</v>
+        <v>0.2147002542574064</v>
       </c>
       <c r="C88">
-        <v>-6234.694248747961</v>
+        <v>-6383.280540290951</v>
       </c>
       <c r="D88">
-        <v>3113.489031555113</v>
+        <v>3084.916499085413</v>
       </c>
       <c r="E88">
-        <v>8216.907372973919</v>
+        <v>8336.92113204721</v>
       </c>
       <c r="F88">
-        <v>10321.18328030307</v>
+        <v>10441.19703937636</v>
       </c>
       <c r="G88">
         <v>973</v>
@@ -8503,37 +8503,37 @@
         <v>623.1</v>
       </c>
       <c r="M88">
-        <v>2072.493602684857</v>
+        <v>2096.592365506774</v>
       </c>
       <c r="N88">
-        <v>-1449.393602684857</v>
+        <v>-1473.492365506774</v>
       </c>
       <c r="O88">
-        <v>-373.9435494926932</v>
+        <v>-380.1610303007478</v>
       </c>
       <c r="P88">
-        <v>-1075.450053192164</v>
+        <v>-1093.331335206026</v>
       </c>
       <c r="Q88">
-        <v>-1003.850053192164</v>
+        <v>-1021.731335206026</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3846954884840299</v>
+        <v>0.4107643722135708</v>
       </c>
       <c r="T88">
-        <v>7.826685646282447</v>
+        <v>8.428738388304176</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.07756829733599188</v>
+        <v>0.07667670771144025</v>
       </c>
       <c r="W88">
-        <v>0.1852242858949328</v>
+        <v>0.1854033170915428</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3006523152557824</v>
+        <v>0.2971965415172102</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2147002542574064</v>
+        <v>0.2162502542574064</v>
       </c>
       <c r="C89">
-        <v>-6383.280540290951</v>
+        <v>-6531.347179627839</v>
       </c>
       <c r="D89">
-        <v>3084.916499085413</v>
+        <v>3056.863618821817</v>
       </c>
       <c r="E89">
-        <v>8336.92113204721</v>
+        <v>8456.934891120502</v>
       </c>
       <c r="F89">
-        <v>10441.19703937636</v>
+        <v>10561.21079844966</v>
       </c>
       <c r="G89">
         <v>973</v>
@@ -8585,37 +8585,37 @@
         <v>623.1</v>
       </c>
       <c r="M89">
-        <v>2096.592365506774</v>
+        <v>2120.691128328691</v>
       </c>
       <c r="N89">
-        <v>-1473.492365506774</v>
+        <v>-1497.591128328691</v>
       </c>
       <c r="O89">
-        <v>-380.1610303007478</v>
+        <v>-386.3785111088023</v>
       </c>
       <c r="P89">
-        <v>-1093.331335206026</v>
+        <v>-1111.212617219889</v>
       </c>
       <c r="Q89">
-        <v>-1021.731335206026</v>
+        <v>-1039.612617219889</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4107643722135708</v>
+        <v>0.4411780698980349</v>
       </c>
       <c r="T89">
-        <v>8.428738388304176</v>
+        <v>9.13113325399619</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.07667670771144025</v>
+        <v>0.0758053814874466</v>
       </c>
       <c r="W89">
-        <v>0.1854033170915428</v>
+        <v>0.1855782793973207</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2971965415172102</v>
+        <v>0.2938193080908783</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2162502542574064</v>
+        <v>0.2178002542574064</v>
       </c>
       <c r="C90">
-        <v>-6531.347179627839</v>
+        <v>-6678.908215474821</v>
       </c>
       <c r="D90">
-        <v>3056.863618821817</v>
+        <v>3029.316342048127</v>
       </c>
       <c r="E90">
-        <v>8456.934891120502</v>
+        <v>8576.948650193794</v>
       </c>
       <c r="F90">
-        <v>10561.21079844966</v>
+        <v>10681.22455752295</v>
       </c>
       <c r="G90">
         <v>973</v>
@@ -8667,37 +8667,37 @@
         <v>623.1</v>
       </c>
       <c r="M90">
-        <v>2120.691128328691</v>
+        <v>2144.789891150608</v>
       </c>
       <c r="N90">
-        <v>-1497.591128328691</v>
+        <v>-1521.689891150608</v>
       </c>
       <c r="O90">
-        <v>-386.3785111088023</v>
+        <v>-392.5959919168569</v>
       </c>
       <c r="P90">
-        <v>-1111.212617219889</v>
+        <v>-1129.093899233751</v>
       </c>
       <c r="Q90">
-        <v>-1039.612617219889</v>
+        <v>-1057.493899233751</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4411780698980349</v>
+        <v>0.4771215307978564</v>
       </c>
       <c r="T90">
-        <v>9.13113325399619</v>
+        <v>9.961236277086753</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.0758053814874466</v>
+        <v>0.07495363562803709</v>
       </c>
       <c r="W90">
-        <v>0.1855782793973207</v>
+        <v>0.1857493099658901</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2938193080908783</v>
+        <v>0.2905179675505313</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2178002542574064</v>
+        <v>0.2193502542574065</v>
       </c>
       <c r="C91">
-        <v>-6678.908215474821</v>
+        <v>-6825.977194664418</v>
       </c>
       <c r="D91">
-        <v>3029.316342048127</v>
+        <v>3002.261121931822</v>
       </c>
       <c r="E91">
-        <v>8576.948650193794</v>
+        <v>8696.962409267086</v>
       </c>
       <c r="F91">
-        <v>10681.22455752295</v>
+        <v>10801.23831659624</v>
       </c>
       <c r="G91">
         <v>973</v>
@@ -8749,37 +8749,37 @@
         <v>623.1</v>
       </c>
       <c r="M91">
-        <v>2144.789891150608</v>
+        <v>2168.888653972525</v>
       </c>
       <c r="N91">
-        <v>-1521.689891150608</v>
+        <v>-1545.788653972525</v>
       </c>
       <c r="O91">
-        <v>-392.5959919168569</v>
+        <v>-398.8134727249115</v>
       </c>
       <c r="P91">
-        <v>-1129.093899233751</v>
+        <v>-1146.975181247614</v>
       </c>
       <c r="Q91">
-        <v>-1057.493899233751</v>
+        <v>-1075.375181247614</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4771215307978564</v>
+        <v>0.520253683877642</v>
       </c>
       <c r="T91">
-        <v>9.961236277086753</v>
+        <v>10.95735990479543</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.07495363562803709</v>
+        <v>0.07412081745439224</v>
       </c>
       <c r="W91">
-        <v>0.1857493099658901</v>
+        <v>0.185916539855158</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2905179675505313</v>
+        <v>0.2872899901333031</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2193502542574065</v>
+        <v>0.2209002542574064</v>
       </c>
       <c r="C92">
-        <v>-6825.977194664418</v>
+        <v>-6972.567184359015</v>
       </c>
       <c r="D92">
-        <v>3002.261121931822</v>
+        <v>2975.684891310517</v>
       </c>
       <c r="E92">
-        <v>8696.962409267086</v>
+        <v>8816.976168340378</v>
       </c>
       <c r="F92">
-        <v>10801.23831659624</v>
+        <v>10921.25207566953</v>
       </c>
       <c r="G92">
         <v>973</v>
@@ -8831,37 +8831,37 @@
         <v>623.1</v>
       </c>
       <c r="M92">
-        <v>2168.888653972525</v>
+        <v>2192.987416794442</v>
       </c>
       <c r="N92">
-        <v>-1545.788653972525</v>
+        <v>-1569.887416794442</v>
       </c>
       <c r="O92">
-        <v>-398.8134727249115</v>
+        <v>-405.0309535329661</v>
       </c>
       <c r="P92">
-        <v>-1146.975181247614</v>
+        <v>-1164.856463261476</v>
       </c>
       <c r="Q92">
-        <v>-1075.375181247614</v>
+        <v>-1093.256463261476</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.520253683877642</v>
+        <v>0.5729707598640467</v>
       </c>
       <c r="T92">
-        <v>10.95735990479543</v>
+        <v>12.17484433866159</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07412081745439224</v>
+        <v>0.07330630297687143</v>
       </c>
       <c r="W92">
-        <v>0.185916539855158</v>
+        <v>0.1860800943622442</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2872899901333031</v>
+        <v>0.2841329572746955</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2209002542574064</v>
+        <v>0.2224502542574064</v>
       </c>
       <c r="C93">
-        <v>-6972.567184359015</v>
+        <v>-7118.690793094966</v>
       </c>
       <c r="D93">
-        <v>2975.684891310517</v>
+        <v>2949.575041647857</v>
       </c>
       <c r="E93">
-        <v>8816.976168340378</v>
+        <v>8936.989927413668</v>
       </c>
       <c r="F93">
-        <v>10921.25207566953</v>
+        <v>11041.26583474282</v>
       </c>
       <c r="G93">
         <v>973</v>
@@ -8913,37 +8913,37 @@
         <v>623.1</v>
       </c>
       <c r="M93">
-        <v>2192.987416794442</v>
+        <v>2217.086179616359</v>
       </c>
       <c r="N93">
-        <v>-1569.887416794442</v>
+        <v>-1593.986179616359</v>
       </c>
       <c r="O93">
-        <v>-405.0309535329661</v>
+        <v>-411.2484343410206</v>
       </c>
       <c r="P93">
-        <v>-1164.856463261476</v>
+        <v>-1182.737745275339</v>
       </c>
       <c r="Q93">
-        <v>-1093.256463261476</v>
+        <v>-1111.137745275339</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5729707598640467</v>
+        <v>0.6388671048470527</v>
       </c>
       <c r="T93">
-        <v>12.17484433866159</v>
+        <v>13.69669988099429</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07330630297687143</v>
+        <v>0.07250949533581849</v>
       </c>
       <c r="W93">
-        <v>0.1860800943622442</v>
+        <v>0.1862400933365677</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2841329572746955</v>
+        <v>0.2810445555651879</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2224502542574064</v>
+        <v>0.2240002542574064</v>
       </c>
       <c r="C94">
-        <v>-7118.690793094966</v>
+        <v>-7264.360190728403</v>
       </c>
       <c r="D94">
-        <v>2949.575041647857</v>
+        <v>2923.919403087711</v>
       </c>
       <c r="E94">
-        <v>8936.989927413668</v>
+        <v>9057.00368648696</v>
       </c>
       <c r="F94">
-        <v>11041.26583474282</v>
+        <v>11161.27959381611</v>
       </c>
       <c r="G94">
         <v>973</v>
@@ -8995,37 +8995,37 @@
         <v>623.1</v>
       </c>
       <c r="M94">
-        <v>2217.086179616359</v>
+        <v>2241.184942438276</v>
       </c>
       <c r="N94">
-        <v>-1593.986179616359</v>
+        <v>-1618.084942438276</v>
       </c>
       <c r="O94">
-        <v>-411.2484343410206</v>
+        <v>-417.4659151490752</v>
       </c>
       <c r="P94">
-        <v>-1182.737745275339</v>
+        <v>-1200.619027289201</v>
       </c>
       <c r="Q94">
-        <v>-1111.137745275339</v>
+        <v>-1129.019027289201</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6388671048470527</v>
+        <v>0.7235909769680603</v>
       </c>
       <c r="T94">
-        <v>13.69669988099429</v>
+        <v>15.65337129256491</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07250949533581849</v>
+        <v>0.07172982334296023</v>
       </c>
       <c r="W94">
-        <v>0.1862400933365677</v>
+        <v>0.1863966514727336</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2810445555651879</v>
+        <v>0.278022571096745</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2240002542574064</v>
+        <v>0.2255502542574064</v>
       </c>
       <c r="C95">
-        <v>-7264.360190728403</v>
+        <v>-7409.587127349116</v>
       </c>
       <c r="D95">
-        <v>2923.919403087711</v>
+        <v>2898.706225540291</v>
       </c>
       <c r="E95">
-        <v>9057.00368648696</v>
+        <v>9177.017445560252</v>
       </c>
       <c r="F95">
-        <v>11161.27959381611</v>
+        <v>11281.29335288941</v>
       </c>
       <c r="G95">
         <v>973</v>
@@ -9077,37 +9077,37 @@
         <v>623.1</v>
       </c>
       <c r="M95">
-        <v>2241.184942438276</v>
+        <v>2265.283705260193</v>
       </c>
       <c r="N95">
-        <v>-1618.084942438276</v>
+        <v>-1642.183705260193</v>
       </c>
       <c r="O95">
-        <v>-417.4659151490752</v>
+        <v>-423.6833959571298</v>
       </c>
       <c r="P95">
-        <v>-1200.619027289201</v>
+        <v>-1218.500309303063</v>
       </c>
       <c r="Q95">
-        <v>-1129.019027289201</v>
+        <v>-1146.900309303063</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7235909769680603</v>
+        <v>0.8365561397960706</v>
       </c>
       <c r="T95">
-        <v>15.65337129256491</v>
+        <v>18.2622665079924</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.07172982334296023</v>
+        <v>0.07096674011590744</v>
       </c>
       <c r="W95">
-        <v>0.1863966514727336</v>
+        <v>0.1865498785847258</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.278022571096745</v>
+        <v>0.2750648841701838</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2255502542574064</v>
+        <v>0.2271002542574064</v>
       </c>
       <c r="C96">
-        <v>-7409.587127349116</v>
+        <v>-7554.382951224195</v>
       </c>
       <c r="D96">
-        <v>2898.706225540291</v>
+        <v>2873.924160738503</v>
       </c>
       <c r="E96">
-        <v>9177.017445560252</v>
+        <v>9297.031204633544</v>
       </c>
       <c r="F96">
-        <v>11281.29335288941</v>
+        <v>11401.3071119627</v>
       </c>
       <c r="G96">
         <v>973</v>
@@ -9159,37 +9159,37 @@
         <v>623.1</v>
       </c>
       <c r="M96">
-        <v>2265.283705260193</v>
+        <v>2289.38246808211</v>
       </c>
       <c r="N96">
-        <v>-1642.183705260193</v>
+        <v>-1666.28246808211</v>
       </c>
       <c r="O96">
-        <v>-423.6833959571298</v>
+        <v>-429.9008767651844</v>
       </c>
       <c r="P96">
-        <v>-1218.500309303063</v>
+        <v>-1236.381591316926</v>
       </c>
       <c r="Q96">
-        <v>-1146.900309303063</v>
+        <v>-1164.781591316926</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8365561397960706</v>
+        <v>0.9947073677552851</v>
       </c>
       <c r="T96">
-        <v>18.2622665079924</v>
+        <v>21.91471980959088</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.07096674011590744</v>
+        <v>0.07021972179889789</v>
       </c>
       <c r="W96">
-        <v>0.1865498785847258</v>
+        <v>0.1866998798627813</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2750648841701838</v>
+        <v>0.2721694643368135</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2271002542574064</v>
+        <v>0.2286502542574065</v>
       </c>
       <c r="C97">
-        <v>-7554.382951224195</v>
+        <v>-7698.758625829053</v>
       </c>
       <c r="D97">
-        <v>2873.924160738503</v>
+        <v>2849.562245206937</v>
       </c>
       <c r="E97">
-        <v>9297.031204633544</v>
+        <v>9417.044963706836</v>
       </c>
       <c r="F97">
-        <v>11401.3071119627</v>
+        <v>11521.32087103599</v>
       </c>
       <c r="G97">
         <v>973</v>
@@ -9241,37 +9241,37 @@
         <v>623.1</v>
       </c>
       <c r="M97">
-        <v>2289.38246808211</v>
+        <v>2313.481230904027</v>
       </c>
       <c r="N97">
-        <v>-1666.28246808211</v>
+        <v>-1690.381230904027</v>
       </c>
       <c r="O97">
-        <v>-429.9008767651844</v>
+        <v>-436.1183575732391</v>
       </c>
       <c r="P97">
-        <v>-1236.381591316926</v>
+        <v>-1254.262873330788</v>
       </c>
       <c r="Q97">
-        <v>-1164.781591316926</v>
+        <v>-1182.662873330788</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9947073677552851</v>
+        <v>1.231934209694107</v>
       </c>
       <c r="T97">
-        <v>21.91471980959088</v>
+        <v>27.39339976198862</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.07021972179889789</v>
+        <v>0.0694882663634927</v>
       </c>
       <c r="W97">
-        <v>0.1866998798627813</v>
+        <v>0.1868467561142107</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2721694643368135</v>
+        <v>0.2693343657499717</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2286502542574064</v>
+        <v>0.2302002542574065</v>
       </c>
       <c r="C98">
-        <v>-7698.758625829052</v>
+        <v>-7842.72474601951</v>
       </c>
       <c r="D98">
-        <v>2849.562245206936</v>
+        <v>2825.60988408977</v>
       </c>
       <c r="E98">
-        <v>9417.044963706834</v>
+        <v>9537.058722780126</v>
       </c>
       <c r="F98">
-        <v>11521.32087103599</v>
+        <v>11641.33463010928</v>
       </c>
       <c r="G98">
         <v>973</v>
@@ -9323,37 +9323,37 @@
         <v>623.1</v>
       </c>
       <c r="M98">
-        <v>2313.481230904027</v>
+        <v>2337.579993725943</v>
       </c>
       <c r="N98">
-        <v>-1690.381230904027</v>
+        <v>-1714.479993725944</v>
       </c>
       <c r="O98">
-        <v>-436.1183575732389</v>
+        <v>-442.3358383812935</v>
       </c>
       <c r="P98">
-        <v>-1254.262873330788</v>
+        <v>-1272.14415534465</v>
       </c>
       <c r="Q98">
-        <v>-1182.662873330788</v>
+        <v>-1200.54415534465</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.231934209694104</v>
+        <v>1.627312279592139</v>
       </c>
       <c r="T98">
-        <v>27.39339976198855</v>
+        <v>36.52453301598473</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.06948826636349272</v>
+        <v>0.06877189248345672</v>
       </c>
       <c r="W98">
-        <v>0.1868467561142107</v>
+        <v>0.1869906039893219</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2693343657499717</v>
+        <v>0.2665577228040957</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2302002542574065</v>
+        <v>0.2317502542574064</v>
       </c>
       <c r="C99">
-        <v>-7842.72474601951</v>
+        <v>-7986.291553395045</v>
       </c>
       <c r="D99">
-        <v>2825.60988408977</v>
+        <v>2802.056835787525</v>
       </c>
       <c r="E99">
-        <v>9537.058722780126</v>
+        <v>9657.072481853416</v>
       </c>
       <c r="F99">
-        <v>11641.33463010928</v>
+        <v>11761.34838918257</v>
       </c>
       <c r="G99">
         <v>973</v>
@@ -9405,37 +9405,37 @@
         <v>623.1</v>
       </c>
       <c r="M99">
-        <v>2337.579993725943</v>
+        <v>2361.67875654786</v>
       </c>
       <c r="N99">
-        <v>-1714.479993725944</v>
+        <v>-1738.57875654786</v>
       </c>
       <c r="O99">
-        <v>-442.3358383812935</v>
+        <v>-448.553319189348</v>
       </c>
       <c r="P99">
-        <v>-1272.14415534465</v>
+        <v>-1290.025437358512</v>
       </c>
       <c r="Q99">
-        <v>-1200.54415534465</v>
+        <v>-1218.425437358512</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.627312279592139</v>
+        <v>2.418068419388208</v>
       </c>
       <c r="T99">
-        <v>36.52453301598473</v>
+        <v>54.78679952397709</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.06877189248345672</v>
+        <v>0.06807013847852349</v>
       </c>
       <c r="W99">
-        <v>0.1869906039893219</v>
+        <v>0.1871315161935125</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2665577228040957</v>
+        <v>0.2638377460407887</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2317502542574064</v>
+        <v>0.2333002542574064</v>
       </c>
       <c r="C100">
-        <v>-7986.291553395045</v>
+        <v>-8129.468950900038</v>
       </c>
       <c r="D100">
-        <v>2802.056835787525</v>
+        <v>2778.893197355824</v>
       </c>
       <c r="E100">
-        <v>9657.072481853416</v>
+        <v>9777.086240926708</v>
       </c>
       <c r="F100">
-        <v>11761.34838918257</v>
+        <v>11881.36214825586</v>
       </c>
       <c r="G100">
         <v>973</v>
@@ -9487,37 +9487,37 @@
         <v>623.1</v>
       </c>
       <c r="M100">
-        <v>2361.67875654786</v>
+        <v>2385.777519369777</v>
       </c>
       <c r="N100">
-        <v>-1738.57875654786</v>
+        <v>-1762.677519369777</v>
       </c>
       <c r="O100">
-        <v>-448.553319189348</v>
+        <v>-454.7707999974025</v>
       </c>
       <c r="P100">
-        <v>-1290.025437358512</v>
+        <v>-1307.906719372375</v>
       </c>
       <c r="Q100">
-        <v>-1218.425437358512</v>
+        <v>-1236.306719372375</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.418068419388208</v>
+        <v>4.790336838776415</v>
       </c>
       <c r="T100">
-        <v>54.78679952397709</v>
+        <v>109.5735990479542</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.06807013847852349</v>
+        <v>0.06738256132217477</v>
       </c>
       <c r="W100">
-        <v>0.1871315161935125</v>
+        <v>0.1872695816865073</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2638377460407887</v>
+        <v>0.2611727183030029</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2333002542574064</v>
-      </c>
-      <c r="C101">
-        <v>-8129.468950900038</v>
-      </c>
-      <c r="D101">
-        <v>2778.893197355824</v>
-      </c>
-      <c r="E101">
-        <v>9777.086240926708</v>
-      </c>
-      <c r="F101">
-        <v>11881.36214825586</v>
-      </c>
-      <c r="G101">
-        <v>973</v>
-      </c>
-      <c r="H101">
-        <v>9897.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>694.7</v>
-      </c>
-      <c r="K101">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="L101">
-        <v>623.1</v>
-      </c>
-      <c r="M101">
-        <v>2385.777519369777</v>
-      </c>
-      <c r="N101">
-        <v>-1762.677519369777</v>
-      </c>
-      <c r="O101">
-        <v>-454.7707999974025</v>
-      </c>
-      <c r="P101">
-        <v>-1307.906719372375</v>
-      </c>
-      <c r="Q101">
-        <v>-1236.306719372375</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.790336838776415</v>
-      </c>
-      <c r="T101">
-        <v>109.5735990479542</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.06738256132217477</v>
-      </c>
-      <c r="W101">
-        <v>0.1872695816865073</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2611727183030029</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
